--- a/python-maps/documentation/CDA2FHIR_elga_eMed_groups.xlsx
+++ b/python-maps/documentation/CDA2FHIR_elga_eMed_groups.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10412"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/maximilian/Documents/BlackTusk/Bundesrechenzentrum/CDA2FHIR/CDA2FHIR/python-maps/documentation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6E25B6B5-83BB-A647-84A7-DDE57329DF57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D6903998-BB95-6D41-A79A-718C304FC4C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30180" yWindow="600" windowWidth="19200" windowHeight="21000" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Section" sheetId="2" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1303" uniqueCount="482">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1293" uniqueCount="477">
   <si>
     <t xml:space="preserve">Status
 </t>
@@ -305,9 +305,6 @@
   </si>
   <si>
     <t>Bsp: "completed"</t>
-  </si>
-  <si>
-    <t>Kann mehr mals vorkommen. ToDO: mit welchen Codes?</t>
   </si>
   <si>
     <t>eR/act/@classCode='ACT'</t>
@@ -898,18 +895,12 @@
     <t>TODO: Prüfen auf nullFlavor</t>
   </si>
   <si>
-    <t>MedicationDispense.dosageInstruction.timing.boundsRange.low</t>
-  </si>
-  <si>
     <t>eR/sA/effectiveTime/high/@value</t>
   </si>
   <si>
     <t>Zeitpunkt des Einnahmeendes</t>
   </si>
   <si>
-    <t>MedicationDispense.dosageInstruction.timing.boundsRange.high</t>
-  </si>
-  <si>
     <t>eR/sA/effectiveTime/width/@value</t>
   </si>
   <si>
@@ -931,9 +922,6 @@
     <t>Periodeneinheit aus VS: Tag, Woche, Monat, Jahr</t>
   </si>
   <si>
-    <t>TODO: Abbildungsunterschiede zwischen allen 4 möglichenn Dosierungsvarianten prüfen</t>
-  </si>
-  <si>
     <t>Dosierungsarten 1 und 3 verwenden normal Dosing (1.3.6.1.4.1.19376.1.5.3.1.4.7.1)</t>
   </si>
   <si>
@@ -1031,20 +1019,6 @@
   </si>
   <si>
     <t>eR/sA/effectiveTime/comp</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Reference! </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>MedicationDispense.dosageInstruction.patientInstruction (String)</t>
-    </r>
   </si>
   <si>
     <r>
@@ -1062,20 +1036,6 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">Referenz auf narrativen Teil! </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Medication.text</t>
-    </r>
-  </si>
-  <si>
-    <r>
       <t xml:space="preserve">Reference! </t>
     </r>
     <r>
@@ -1110,9 +1070,6 @@
     <t>Erstes Datum des entsprechenden Wochentags nach Einnahmebeginn.</t>
   </si>
   <si>
-    <t xml:space="preserve">TODO: IN CDA wird Wochentag der regelmäßigen Einnahme durch genaues Datum anstatt Wochentag selbst angegeben. Klären, ob dies unverändert in FHIR übernommen werden soll oder über Datum auf Wochentag zugegriffen und dieser dann explizit gesetzt werden soll. </t>
-  </si>
-  <si>
     <t>http://hl7.org/fhir/ValueSet/timing-abbreviation</t>
   </si>
   <si>
@@ -1201,9 +1158,6 @@
     <t>eR/act/code='PINSTRUCT'</t>
   </si>
   <si>
-    <t>Kann mehrmals vorkommen. ToDO: mit welchen Codes?</t>
-  </si>
-  <si>
     <t>eR/act/entryRelationship/@typeCode='SUBJ'</t>
   </si>
   <si>
@@ -1667,6 +1621,15 @@
   </si>
   <si>
     <t>NA -&gt; Arznei ist magistrale Zubereitung</t>
+  </si>
+  <si>
+    <t>MedicationDispense.dosageInstruction.timing.boundsPeriod.low</t>
+  </si>
+  <si>
+    <t>MedicationDispense.dosageInstruction.timing.boundsPeriod.high</t>
+  </si>
+  <si>
+    <t>Das Wert kommt im Text-Element. Wird nicht als Ganzes gemappt, da stattdessen die darin enthaltenen Codes einzeln gemappt werden.</t>
   </si>
 </sst>
 </file>
@@ -2540,6 +2503,7 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="19" fillId="17" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="19" fillId="17" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="19" fillId="17" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -2574,7 +2538,6 @@
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -3162,7 +3125,7 @@
       <c r="K5" s="7"/>
       <c r="L5" s="20"/>
       <c r="M5" s="7" t="s">
-        <v>474</v>
+        <v>466</v>
       </c>
       <c r="N5" s="7"/>
     </row>
@@ -3233,7 +3196,7 @@
     <col min="10" max="10" width="23.1640625" style="143" customWidth="1"/>
     <col min="11" max="11" width="9.1640625" style="93" customWidth="1"/>
     <col min="12" max="12" width="0.1640625" style="108" customWidth="1"/>
-    <col min="13" max="13" width="61.5" style="93" customWidth="1"/>
+    <col min="13" max="13" width="69" style="93" customWidth="1"/>
     <col min="14" max="14" width="13.83203125" customWidth="1"/>
     <col min="15" max="15" width="36.83203125" customWidth="1"/>
     <col min="16" max="16" width="36.5" customWidth="1"/>
@@ -3319,7 +3282,7 @@
         <v>35</v>
       </c>
       <c r="D3" s="137" t="s">
-        <v>354</v>
+        <v>346</v>
       </c>
       <c r="E3" s="82"/>
       <c r="F3" s="82"/>
@@ -3343,7 +3306,7 @@
         <v>36</v>
       </c>
       <c r="D4" s="84" t="s">
-        <v>353</v>
+        <v>345</v>
       </c>
       <c r="E4" s="82"/>
       <c r="F4" s="82"/>
@@ -3367,7 +3330,7 @@
         <v>36</v>
       </c>
       <c r="D5" s="92" t="s">
-        <v>352</v>
+        <v>344</v>
       </c>
       <c r="E5" s="82"/>
       <c r="F5" s="82"/>
@@ -3393,7 +3356,7 @@
         <v>36</v>
       </c>
       <c r="D6" s="86" t="s">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="E6" s="82"/>
       <c r="F6" s="82"/>
@@ -3419,7 +3382,7 @@
         <v>36</v>
       </c>
       <c r="D7" s="86" t="s">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="E7" s="82"/>
       <c r="F7" s="82"/>
@@ -3445,7 +3408,7 @@
         <v>36</v>
       </c>
       <c r="D8" s="86" t="s">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="E8" s="82"/>
       <c r="F8" s="87"/>
@@ -3471,7 +3434,7 @@
         <v>36</v>
       </c>
       <c r="D9" s="86" t="s">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="E9" s="82"/>
       <c r="F9" s="87"/>
@@ -3495,7 +3458,7 @@
         <v>36</v>
       </c>
       <c r="D10" s="81" t="s">
-        <v>348</v>
+        <v>340</v>
       </c>
       <c r="E10" s="87"/>
       <c r="F10" s="87"/>
@@ -3521,7 +3484,7 @@
         <v>38</v>
       </c>
       <c r="D11" s="81" t="s">
-        <v>349</v>
+        <v>341</v>
       </c>
       <c r="E11" s="87"/>
       <c r="F11" s="87"/>
@@ -3547,7 +3510,7 @@
         <v>40</v>
       </c>
       <c r="D12" s="92" t="s">
-        <v>350</v>
+        <v>342</v>
       </c>
       <c r="E12" s="82"/>
       <c r="F12" s="93" t="s">
@@ -3561,7 +3524,7 @@
         <v>43</v>
       </c>
       <c r="J12" s="83" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="K12" s="83"/>
       <c r="L12" s="83"/>
@@ -3581,13 +3544,13 @@
         <v>36</v>
       </c>
       <c r="D13" s="92" t="s">
-        <v>351</v>
+        <v>343</v>
       </c>
       <c r="E13" s="82"/>
       <c r="G13" s="87"/>
       <c r="H13" s="95"/>
       <c r="I13" s="81" t="s">
-        <v>362</v>
+        <v>354</v>
       </c>
       <c r="J13" s="94"/>
       <c r="K13" s="83"/>
@@ -3606,7 +3569,7 @@
         <v>36</v>
       </c>
       <c r="D14" s="84" t="s">
-        <v>475</v>
+        <v>467</v>
       </c>
       <c r="E14" s="82"/>
       <c r="F14" s="87"/>
@@ -3616,7 +3579,7 @@
         <v>45</v>
       </c>
       <c r="J14" s="94" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="K14" s="83"/>
       <c r="L14" s="83"/>
@@ -3628,21 +3591,21 @@
       <c r="P14" s="82"/>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A15" s="153" t="s">
-        <v>451</v>
-      </c>
-      <c r="B15" s="153"/>
-      <c r="C15" s="153"/>
-      <c r="D15" s="154"/>
-      <c r="E15" s="154"/>
-      <c r="F15" s="154"/>
-      <c r="G15" s="154"/>
-      <c r="H15" s="153"/>
-      <c r="I15" s="155"/>
-      <c r="J15" s="153"/>
-      <c r="K15" s="153"/>
-      <c r="L15" s="153"/>
-      <c r="M15" s="153"/>
+      <c r="A15" s="154" t="s">
+        <v>443</v>
+      </c>
+      <c r="B15" s="154"/>
+      <c r="C15" s="154"/>
+      <c r="D15" s="155"/>
+      <c r="E15" s="155"/>
+      <c r="F15" s="155"/>
+      <c r="G15" s="155"/>
+      <c r="H15" s="154"/>
+      <c r="I15" s="156"/>
+      <c r="J15" s="154"/>
+      <c r="K15" s="154"/>
+      <c r="L15" s="154"/>
+      <c r="M15" s="154"/>
       <c r="N15" s="82"/>
       <c r="O15" s="82"/>
       <c r="P15" s="82"/>
@@ -3656,7 +3619,7 @@
         <v>36</v>
       </c>
       <c r="D16" s="81" t="s">
-        <v>424</v>
+        <v>416</v>
       </c>
       <c r="E16" s="82"/>
       <c r="F16" s="87"/>
@@ -3680,7 +3643,7 @@
         <v>36</v>
       </c>
       <c r="D17" s="97" t="s">
-        <v>425</v>
+        <v>417</v>
       </c>
       <c r="E17" s="82"/>
       <c r="F17" s="87"/>
@@ -3704,7 +3667,7 @@
         <v>36</v>
       </c>
       <c r="D18" s="97" t="s">
-        <v>425</v>
+        <v>417</v>
       </c>
       <c r="E18" s="82"/>
       <c r="F18" s="87"/>
@@ -3728,7 +3691,7 @@
         <v>36</v>
       </c>
       <c r="D19" s="81" t="s">
-        <v>426</v>
+        <v>418</v>
       </c>
       <c r="E19" s="82"/>
       <c r="F19" s="87"/>
@@ -3752,7 +3715,7 @@
         <v>36</v>
       </c>
       <c r="D20" s="81" t="s">
-        <v>427</v>
+        <v>419</v>
       </c>
       <c r="E20" s="82"/>
       <c r="F20" s="87"/>
@@ -3776,7 +3739,7 @@
         <v>36</v>
       </c>
       <c r="D21" s="97" t="s">
-        <v>428</v>
+        <v>420</v>
       </c>
       <c r="E21" s="82"/>
       <c r="F21" s="87"/>
@@ -3800,7 +3763,7 @@
         <v>36</v>
       </c>
       <c r="D22" s="81" t="s">
-        <v>428</v>
+        <v>420</v>
       </c>
       <c r="E22" s="82"/>
       <c r="F22" s="87"/>
@@ -3824,7 +3787,7 @@
         <v>36</v>
       </c>
       <c r="D23" s="81" t="s">
-        <v>429</v>
+        <v>421</v>
       </c>
       <c r="E23" s="82"/>
       <c r="F23" s="87"/>
@@ -3839,7 +3802,7 @@
       <c r="K23" s="83"/>
       <c r="L23" s="82"/>
       <c r="M23" s="81" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="N23" s="82"/>
       <c r="O23" s="82"/>
@@ -3854,17 +3817,17 @@
         <v>36</v>
       </c>
       <c r="D24" s="81" t="s">
-        <v>480</v>
+        <v>472</v>
       </c>
       <c r="E24" s="82"/>
       <c r="F24" s="87"/>
       <c r="G24" s="87"/>
       <c r="H24" s="82"/>
       <c r="I24" s="81" t="s">
-        <v>481</v>
+        <v>473</v>
       </c>
       <c r="J24" s="83" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="K24" s="83"/>
       <c r="L24" s="82"/>
@@ -3882,7 +3845,7 @@
         <v>36</v>
       </c>
       <c r="D25" s="81" t="s">
-        <v>430</v>
+        <v>422</v>
       </c>
       <c r="E25" s="82"/>
       <c r="F25" s="87"/>
@@ -3897,7 +3860,7 @@
       <c r="K25" s="83"/>
       <c r="L25" s="82"/>
       <c r="M25" s="81" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="N25" s="82"/>
       <c r="O25" s="82"/>
@@ -3912,7 +3875,7 @@
         <v>36</v>
       </c>
       <c r="D26" s="81" t="s">
-        <v>431</v>
+        <v>423</v>
       </c>
       <c r="E26" s="82"/>
       <c r="F26" s="87"/>
@@ -3940,7 +3903,7 @@
         <v>36</v>
       </c>
       <c r="D27" s="81" t="s">
-        <v>432</v>
+        <v>424</v>
       </c>
       <c r="E27" s="82"/>
       <c r="F27" s="93" t="s">
@@ -3970,7 +3933,7 @@
         <v>36</v>
       </c>
       <c r="D28" s="81" t="s">
-        <v>433</v>
+        <v>425</v>
       </c>
       <c r="E28" s="82"/>
       <c r="F28" s="87"/>
@@ -3994,7 +3957,7 @@
         <v>36</v>
       </c>
       <c r="D29" s="81" t="s">
-        <v>434</v>
+        <v>426</v>
       </c>
       <c r="E29" s="82"/>
       <c r="F29" s="87"/>
@@ -4018,7 +3981,7 @@
         <v>36</v>
       </c>
       <c r="D30" s="81" t="s">
-        <v>435</v>
+        <v>427</v>
       </c>
       <c r="E30" s="82"/>
       <c r="F30" s="87"/>
@@ -4046,7 +4009,7 @@
         <v>36</v>
       </c>
       <c r="D31" s="81" t="s">
-        <v>436</v>
+        <v>428</v>
       </c>
       <c r="E31" s="82"/>
       <c r="F31" s="87"/>
@@ -4070,7 +4033,7 @@
         <v>36</v>
       </c>
       <c r="D32" s="81" t="s">
-        <v>437</v>
+        <v>429</v>
       </c>
       <c r="E32" s="82"/>
       <c r="F32" s="87"/>
@@ -4094,7 +4057,7 @@
         <v>36</v>
       </c>
       <c r="D33" s="81" t="s">
-        <v>438</v>
+        <v>430</v>
       </c>
       <c r="E33" s="82"/>
       <c r="F33" s="87"/>
@@ -4118,7 +4081,7 @@
         <v>36</v>
       </c>
       <c r="D34" s="81" t="s">
-        <v>439</v>
+        <v>431</v>
       </c>
       <c r="E34" s="82"/>
       <c r="F34" s="87"/>
@@ -4148,7 +4111,7 @@
         <v>36</v>
       </c>
       <c r="D35" s="81" t="s">
-        <v>440</v>
+        <v>432</v>
       </c>
       <c r="E35" s="82"/>
       <c r="F35" s="87"/>
@@ -4178,7 +4141,7 @@
         <v>36</v>
       </c>
       <c r="D36" s="81" t="s">
-        <v>441</v>
+        <v>433</v>
       </c>
       <c r="E36" s="82"/>
       <c r="F36" s="87"/>
@@ -4206,7 +4169,7 @@
         <v>36</v>
       </c>
       <c r="D37" s="81" t="s">
-        <v>439</v>
+        <v>431</v>
       </c>
       <c r="E37" s="82"/>
       <c r="F37" s="87" t="s">
@@ -4238,7 +4201,7 @@
         <v>36</v>
       </c>
       <c r="D38" s="81" t="s">
-        <v>441</v>
+        <v>433</v>
       </c>
       <c r="E38" s="82"/>
       <c r="F38" s="87"/>
@@ -4258,19 +4221,19 @@
       <c r="P38" s="82"/>
     </row>
     <row r="39" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A39" s="150" t="s">
-        <v>452</v>
-      </c>
-      <c r="B39" s="151"/>
-      <c r="C39" s="151"/>
-      <c r="D39" s="151"/>
-      <c r="E39" s="151"/>
-      <c r="F39" s="151"/>
-      <c r="G39" s="151"/>
-      <c r="H39" s="151"/>
-      <c r="I39" s="151"/>
-      <c r="J39" s="151"/>
-      <c r="K39" s="152"/>
+      <c r="A39" s="151" t="s">
+        <v>444</v>
+      </c>
+      <c r="B39" s="152"/>
+      <c r="C39" s="152"/>
+      <c r="D39" s="152"/>
+      <c r="E39" s="152"/>
+      <c r="F39" s="152"/>
+      <c r="G39" s="152"/>
+      <c r="H39" s="152"/>
+      <c r="I39" s="152"/>
+      <c r="J39" s="152"/>
+      <c r="K39" s="153"/>
       <c r="L39" s="100"/>
       <c r="M39" s="100"/>
       <c r="N39" s="82"/>
@@ -4283,17 +4246,17 @@
       </c>
       <c r="B40" s="94"/>
       <c r="C40" s="83" t="s">
-        <v>476</v>
+        <v>468</v>
       </c>
       <c r="D40" s="81" t="s">
-        <v>477</v>
+        <v>469</v>
       </c>
       <c r="E40" s="82"/>
       <c r="F40" s="87"/>
       <c r="G40" s="87"/>
       <c r="H40" s="82"/>
       <c r="I40" s="85" t="s">
-        <v>454</v>
+        <v>446</v>
       </c>
       <c r="J40" s="83"/>
       <c r="K40" s="83"/>
@@ -4309,20 +4272,20 @@
       </c>
       <c r="B41" s="94"/>
       <c r="C41" s="83" t="s">
-        <v>476</v>
+        <v>468</v>
       </c>
       <c r="D41" s="81" t="s">
-        <v>478</v>
+        <v>470</v>
       </c>
       <c r="E41" s="82"/>
       <c r="F41" s="87"/>
       <c r="G41" s="87"/>
       <c r="H41" s="82"/>
       <c r="I41" s="85" t="s">
-        <v>479</v>
+        <v>471</v>
       </c>
       <c r="J41" s="83" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="K41" s="83"/>
       <c r="L41" s="82"/>
@@ -4481,7 +4444,7 @@
       <c r="K47" s="83"/>
       <c r="L47" s="82"/>
       <c r="M47" s="81" t="s">
-        <v>456</v>
+        <v>448</v>
       </c>
       <c r="N47" s="82"/>
       <c r="O47" s="82"/>
@@ -4507,26 +4470,26 @@
       <c r="K48" s="83"/>
       <c r="L48" s="82"/>
       <c r="M48" s="85" t="s">
-        <v>457</v>
+        <v>449</v>
       </c>
       <c r="N48" s="82"/>
       <c r="O48" s="82"/>
       <c r="P48" s="82"/>
     </row>
     <row r="49" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A49" s="150" t="s">
-        <v>202</v>
-      </c>
-      <c r="B49" s="151"/>
-      <c r="C49" s="151"/>
-      <c r="D49" s="151"/>
-      <c r="E49" s="151"/>
-      <c r="F49" s="151"/>
-      <c r="G49" s="151"/>
-      <c r="H49" s="151"/>
-      <c r="I49" s="151"/>
-      <c r="J49" s="151"/>
-      <c r="K49" s="151"/>
+      <c r="A49" s="151" t="s">
+        <v>201</v>
+      </c>
+      <c r="B49" s="152"/>
+      <c r="C49" s="152"/>
+      <c r="D49" s="152"/>
+      <c r="E49" s="152"/>
+      <c r="F49" s="152"/>
+      <c r="G49" s="152"/>
+      <c r="H49" s="152"/>
+      <c r="I49" s="152"/>
+      <c r="J49" s="152"/>
+      <c r="K49" s="152"/>
       <c r="L49" s="101"/>
       <c r="M49" s="100"/>
       <c r="N49" s="82"/>
@@ -4683,7 +4646,7 @@
       <c r="K55" s="83"/>
       <c r="L55" s="82"/>
       <c r="M55" s="81" t="s">
-        <v>456</v>
+        <v>448</v>
       </c>
       <c r="N55" s="82"/>
       <c r="O55" s="82"/>
@@ -4709,28 +4672,28 @@
       <c r="K56" s="83"/>
       <c r="L56" s="82"/>
       <c r="M56" s="85" t="s">
-        <v>457</v>
+        <v>449</v>
       </c>
       <c r="N56" s="82"/>
       <c r="O56" s="82"/>
       <c r="P56" s="82"/>
     </row>
     <row r="57" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A57" s="158" t="s">
-        <v>203</v>
-      </c>
-      <c r="B57" s="148"/>
-      <c r="C57" s="148"/>
-      <c r="D57" s="148"/>
-      <c r="E57" s="148"/>
-      <c r="F57" s="148"/>
-      <c r="G57" s="148"/>
-      <c r="H57" s="148"/>
-      <c r="I57" s="159"/>
-      <c r="J57" s="159"/>
-      <c r="K57" s="159"/>
-      <c r="L57" s="148"/>
-      <c r="M57" s="160"/>
+      <c r="A57" s="159" t="s">
+        <v>202</v>
+      </c>
+      <c r="B57" s="149"/>
+      <c r="C57" s="149"/>
+      <c r="D57" s="149"/>
+      <c r="E57" s="149"/>
+      <c r="F57" s="149"/>
+      <c r="G57" s="149"/>
+      <c r="H57" s="149"/>
+      <c r="I57" s="160"/>
+      <c r="J57" s="160"/>
+      <c r="K57" s="160"/>
+      <c r="L57" s="149"/>
+      <c r="M57" s="161"/>
       <c r="N57" s="82"/>
       <c r="O57" s="82"/>
       <c r="P57" s="82"/>
@@ -4744,7 +4707,7 @@
         <v>36</v>
       </c>
       <c r="D58" s="85" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="E58" s="82"/>
       <c r="F58" s="87"/>
@@ -4759,7 +4722,7 @@
       <c r="O58" s="82"/>
       <c r="P58" s="82"/>
     </row>
-    <row r="59" spans="1:16" ht="34" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:16" ht="17" x14ac:dyDescent="0.2">
       <c r="A59" s="114" t="s">
         <v>26</v>
       </c>
@@ -4768,7 +4731,7 @@
         <v>36</v>
       </c>
       <c r="D59" s="81" t="s">
-        <v>336</v>
+        <v>328</v>
       </c>
       <c r="E59" s="82"/>
       <c r="F59" s="87"/>
@@ -4779,22 +4742,22 @@
       <c r="K59" s="83"/>
       <c r="L59" s="82"/>
       <c r="M59" s="85" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="N59" s="82"/>
       <c r="O59" s="82"/>
       <c r="P59" s="82"/>
     </row>
-    <row r="60" spans="1:16" ht="34" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:16" ht="17" x14ac:dyDescent="0.2">
       <c r="A60" s="114" t="s">
         <v>26</v>
       </c>
       <c r="B60" s="83"/>
       <c r="C60" s="83" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D60" s="81" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="E60" s="82"/>
       <c r="F60" s="87"/>
@@ -4805,7 +4768,7 @@
       <c r="K60" s="83"/>
       <c r="L60" s="82"/>
       <c r="M60" s="85" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="N60" s="82"/>
       <c r="O60" s="82"/>
@@ -4813,7 +4776,7 @@
     </row>
     <row r="61" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A61" s="120" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B61" s="102"/>
       <c r="C61" s="102"/>
@@ -4823,10 +4786,10 @@
       <c r="G61" s="103"/>
       <c r="H61" s="103"/>
       <c r="I61" s="102"/>
-      <c r="J61" s="147"/>
-      <c r="K61" s="147"/>
-      <c r="L61" s="148"/>
-      <c r="M61" s="149"/>
+      <c r="J61" s="148"/>
+      <c r="K61" s="148"/>
+      <c r="L61" s="149"/>
+      <c r="M61" s="150"/>
       <c r="N61" s="82"/>
       <c r="O61" s="82"/>
       <c r="P61" s="82"/>
@@ -4840,7 +4803,7 @@
         <v>36</v>
       </c>
       <c r="D62" s="81" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E62" s="82"/>
       <c r="F62" s="87"/>
@@ -4864,7 +4827,7 @@
         <v>36</v>
       </c>
       <c r="D63" s="84" t="s">
-        <v>325</v>
+        <v>318</v>
       </c>
       <c r="E63" s="82"/>
       <c r="F63" s="87"/>
@@ -4888,7 +4851,7 @@
         <v>36</v>
       </c>
       <c r="D64" s="81" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E64" s="82"/>
       <c r="F64" s="87"/>
@@ -4912,7 +4875,7 @@
         <v>36</v>
       </c>
       <c r="D65" s="81" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E65" s="82"/>
       <c r="F65" s="87"/>
@@ -4922,7 +4885,6 @@
       <c r="J65" s="83"/>
       <c r="K65" s="83"/>
       <c r="L65" s="82"/>
-      <c r="M65" s="83"/>
       <c r="N65" s="82"/>
       <c r="O65" s="82"/>
       <c r="P65" s="82"/>
@@ -4938,7 +4900,7 @@
         <v>36</v>
       </c>
       <c r="D66" s="81" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="E66" s="82"/>
       <c r="F66" s="87"/>
@@ -4964,7 +4926,7 @@
         <v>36</v>
       </c>
       <c r="D67" s="81" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="E67" s="82"/>
       <c r="F67" s="87"/>
@@ -4988,7 +4950,7 @@
         <v>36</v>
       </c>
       <c r="D68" s="81" t="s">
-        <v>326</v>
+        <v>319</v>
       </c>
       <c r="E68" s="82"/>
       <c r="F68" s="87"/>
@@ -4997,7 +4959,7 @@
       </c>
       <c r="H68" s="82"/>
       <c r="I68" s="81" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="J68" s="83"/>
       <c r="K68" s="83"/>
@@ -5008,28 +4970,26 @@
       <c r="P68" s="82"/>
     </row>
     <row r="69" spans="1:16" ht="34" x14ac:dyDescent="0.2">
-      <c r="A69" s="114" t="s">
-        <v>26</v>
+      <c r="A69" s="113" t="s">
+        <v>16</v>
       </c>
       <c r="B69" s="121"/>
       <c r="C69" s="83" t="s">
         <v>36</v>
       </c>
       <c r="D69" s="81" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E69" s="82"/>
       <c r="G69" s="87"/>
       <c r="H69" s="82"/>
       <c r="I69" s="86" t="s">
-        <v>86</v>
+        <v>476</v>
       </c>
       <c r="J69" s="94"/>
       <c r="K69" s="83"/>
       <c r="L69" s="82"/>
-      <c r="M69" s="104" t="s">
-        <v>287</v>
-      </c>
+      <c r="M69" s="104"/>
       <c r="N69" s="82"/>
       <c r="O69" s="82"/>
       <c r="P69" s="82"/>
@@ -5043,7 +5003,7 @@
         <v>18</v>
       </c>
       <c r="D70" s="81" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E70" s="82"/>
       <c r="F70" s="87"/>
@@ -5066,18 +5026,16 @@
       </c>
       <c r="B71" s="121"/>
       <c r="C71" s="83" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="D71" s="81" t="s">
-        <v>328</v>
+        <v>320</v>
       </c>
       <c r="E71" s="82"/>
       <c r="F71" s="87"/>
       <c r="G71" s="87"/>
       <c r="H71" s="82"/>
-      <c r="I71" s="81" t="s">
-        <v>327</v>
-      </c>
+      <c r="I71" s="81"/>
       <c r="J71" s="83"/>
       <c r="K71" s="83"/>
       <c r="L71" s="82"/>
@@ -5095,7 +5053,7 @@
         <v>36</v>
       </c>
       <c r="D72" s="81" t="s">
-        <v>329</v>
+        <v>321</v>
       </c>
       <c r="E72" s="82"/>
       <c r="F72" s="87"/>
@@ -5119,7 +5077,7 @@
         <v>36</v>
       </c>
       <c r="D73" s="81" t="s">
-        <v>330</v>
+        <v>322</v>
       </c>
       <c r="E73" s="82"/>
       <c r="F73" s="87"/>
@@ -5143,7 +5101,7 @@
         <v>36</v>
       </c>
       <c r="D74" s="81" t="s">
-        <v>331</v>
+        <v>323</v>
       </c>
       <c r="E74" s="82"/>
       <c r="F74" s="87"/>
@@ -5169,7 +5127,7 @@
         <v>36</v>
       </c>
       <c r="D75" s="81" t="s">
-        <v>332</v>
+        <v>324</v>
       </c>
       <c r="E75" s="82"/>
       <c r="F75" s="87"/>
@@ -5193,18 +5151,18 @@
         <v>36</v>
       </c>
       <c r="D76" s="81" t="s">
-        <v>333</v>
+        <v>325</v>
       </c>
       <c r="E76" s="82"/>
       <c r="F76" s="93" t="s">
+        <v>91</v>
+      </c>
+      <c r="G76" s="87" t="s">
         <v>92</v>
-      </c>
-      <c r="G76" s="87" t="s">
-        <v>93</v>
       </c>
       <c r="H76" s="82"/>
       <c r="I76" s="85" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="J76" s="83"/>
       <c r="K76" s="83"/>
@@ -5214,7 +5172,7 @@
       <c r="O76" s="82"/>
       <c r="P76" s="82"/>
     </row>
-    <row r="77" spans="1:16" ht="68" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:16" ht="51" x14ac:dyDescent="0.2">
       <c r="A77" s="114" t="s">
         <v>26</v>
       </c>
@@ -5223,7 +5181,7 @@
         <v>36</v>
       </c>
       <c r="D77" s="81" t="s">
-        <v>334</v>
+        <v>326</v>
       </c>
       <c r="E77" s="82"/>
       <c r="G77" s="87"/>
@@ -5235,7 +5193,7 @@
       <c r="K77" s="83"/>
       <c r="L77" s="82"/>
       <c r="M77" s="106" t="s">
-        <v>288</v>
+        <v>283</v>
       </c>
       <c r="N77" s="82"/>
       <c r="O77" s="82"/>
@@ -5250,7 +5208,7 @@
         <v>36</v>
       </c>
       <c r="D78" s="81" t="s">
-        <v>335</v>
+        <v>327</v>
       </c>
       <c r="E78" s="82"/>
       <c r="F78" s="87"/>
@@ -5267,7 +5225,7 @@
     </row>
     <row r="79" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A79" s="120" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B79" s="102"/>
       <c r="C79" s="102"/>
@@ -5277,10 +5235,10 @@
       <c r="G79" s="103"/>
       <c r="H79" s="103"/>
       <c r="I79" s="102"/>
-      <c r="J79" s="147"/>
-      <c r="K79" s="147"/>
-      <c r="L79" s="148"/>
-      <c r="M79" s="149"/>
+      <c r="J79" s="148"/>
+      <c r="K79" s="148"/>
+      <c r="L79" s="149"/>
+      <c r="M79" s="150"/>
       <c r="N79" s="82"/>
       <c r="O79" s="82"/>
       <c r="P79" s="82"/>
@@ -5294,7 +5252,7 @@
         <v>36</v>
       </c>
       <c r="D80" s="81" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E80" s="82"/>
       <c r="F80" s="87"/>
@@ -5318,7 +5276,7 @@
         <v>36</v>
       </c>
       <c r="D81" s="84" t="s">
-        <v>325</v>
+        <v>318</v>
       </c>
       <c r="E81" s="82"/>
       <c r="F81" s="87"/>
@@ -5342,7 +5300,7 @@
         <v>36</v>
       </c>
       <c r="D82" s="81" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E82" s="82"/>
       <c r="F82" s="87"/>
@@ -5366,7 +5324,7 @@
         <v>36</v>
       </c>
       <c r="D83" s="81" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E83" s="82"/>
       <c r="F83" s="87"/>
@@ -5392,7 +5350,7 @@
         <v>36</v>
       </c>
       <c r="D84" s="81" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="E84" s="82"/>
       <c r="F84" s="87"/>
@@ -5418,7 +5376,7 @@
         <v>36</v>
       </c>
       <c r="D85" s="81" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="E85" s="82"/>
       <c r="F85" s="87"/>
@@ -5442,7 +5400,7 @@
         <v>36</v>
       </c>
       <c r="D86" s="81" t="s">
-        <v>338</v>
+        <v>330</v>
       </c>
       <c r="E86" s="82"/>
       <c r="F86" s="87"/>
@@ -5451,7 +5409,7 @@
       </c>
       <c r="H86" s="82"/>
       <c r="I86" s="81" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="J86" s="83"/>
       <c r="K86" s="83"/>
@@ -5461,29 +5419,27 @@
       <c r="O86" s="82"/>
       <c r="P86" s="82"/>
     </row>
-    <row r="87" spans="1:16" ht="17" x14ac:dyDescent="0.2">
-      <c r="A87" s="114" t="s">
-        <v>26</v>
+    <row r="87" spans="1:16" ht="34" x14ac:dyDescent="0.2">
+      <c r="A87" s="113" t="s">
+        <v>16</v>
       </c>
       <c r="B87" s="121"/>
       <c r="C87" s="83" t="s">
         <v>36</v>
       </c>
       <c r="D87" s="81" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E87" s="82"/>
       <c r="G87" s="87"/>
       <c r="H87" s="82"/>
       <c r="I87" s="86" t="s">
-        <v>86</v>
+        <v>476</v>
       </c>
       <c r="J87" s="94"/>
       <c r="K87" s="83"/>
       <c r="L87" s="82"/>
-      <c r="M87" s="104" t="s">
-        <v>289</v>
-      </c>
+      <c r="M87" s="104"/>
       <c r="N87" s="82"/>
       <c r="O87" s="82"/>
       <c r="P87" s="82"/>
@@ -5497,7 +5453,7 @@
         <v>18</v>
       </c>
       <c r="D88" s="81" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E88" s="82"/>
       <c r="F88" s="87"/>
@@ -5520,18 +5476,16 @@
       </c>
       <c r="B89" s="121"/>
       <c r="C89" s="83" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="D89" s="81" t="s">
-        <v>328</v>
+        <v>320</v>
       </c>
       <c r="E89" s="82"/>
       <c r="F89" s="87"/>
       <c r="G89" s="87"/>
       <c r="H89" s="82"/>
-      <c r="I89" s="81" t="s">
-        <v>88</v>
-      </c>
+      <c r="I89" s="81"/>
       <c r="J89" s="83"/>
       <c r="K89" s="83"/>
       <c r="L89" s="82"/>
@@ -5549,7 +5503,7 @@
         <v>36</v>
       </c>
       <c r="D90" s="81" t="s">
-        <v>329</v>
+        <v>321</v>
       </c>
       <c r="E90" s="82"/>
       <c r="F90" s="87"/>
@@ -5573,7 +5527,7 @@
         <v>36</v>
       </c>
       <c r="D91" s="81" t="s">
-        <v>330</v>
+        <v>322</v>
       </c>
       <c r="E91" s="82"/>
       <c r="F91" s="87"/>
@@ -5597,7 +5551,7 @@
         <v>36</v>
       </c>
       <c r="D92" s="81" t="s">
-        <v>331</v>
+        <v>323</v>
       </c>
       <c r="E92" s="82"/>
       <c r="F92" s="87"/>
@@ -5623,7 +5577,7 @@
         <v>36</v>
       </c>
       <c r="D93" s="81" t="s">
-        <v>332</v>
+        <v>324</v>
       </c>
       <c r="E93" s="82"/>
       <c r="F93" s="87"/>
@@ -5647,18 +5601,18 @@
         <v>36</v>
       </c>
       <c r="D94" s="81" t="s">
-        <v>333</v>
+        <v>325</v>
       </c>
       <c r="E94" s="82"/>
       <c r="F94" s="93" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="G94" s="87" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H94" s="82"/>
       <c r="I94" s="85" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="J94" s="83"/>
       <c r="K94" s="83"/>
@@ -5677,7 +5631,7 @@
         <v>36</v>
       </c>
       <c r="D95" s="81" t="s">
-        <v>334</v>
+        <v>326</v>
       </c>
       <c r="E95" s="82"/>
       <c r="G95" s="87"/>
@@ -5689,7 +5643,7 @@
       <c r="K95" s="83"/>
       <c r="L95" s="82"/>
       <c r="M95" s="106" t="s">
-        <v>290</v>
+        <v>284</v>
       </c>
       <c r="N95" s="82"/>
       <c r="O95" s="82"/>
@@ -5704,7 +5658,7 @@
         <v>36</v>
       </c>
       <c r="D96" s="81" t="s">
-        <v>335</v>
+        <v>327</v>
       </c>
       <c r="E96" s="82"/>
       <c r="F96" s="87"/>
@@ -5721,7 +5675,7 @@
     </row>
     <row r="97" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A97" s="117" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B97" s="103"/>
       <c r="C97" s="103"/>
@@ -5748,7 +5702,7 @@
         <v>36</v>
       </c>
       <c r="D98" s="123" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="I98" s="83"/>
       <c r="J98" s="83"/>
@@ -5767,7 +5721,7 @@
         <v>36</v>
       </c>
       <c r="D99" s="124" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="I99" s="83"/>
       <c r="J99" s="83"/>
@@ -5786,7 +5740,7 @@
         <v>36</v>
       </c>
       <c r="D100" s="123" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E100" s="82"/>
       <c r="F100" s="87"/>
@@ -5810,7 +5764,7 @@
         <v>36</v>
       </c>
       <c r="D101" s="123" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E101" s="82"/>
       <c r="F101" s="87"/>
@@ -5836,7 +5790,7 @@
         <v>36</v>
       </c>
       <c r="D102" s="123" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E102" s="82"/>
       <c r="F102" s="87"/>
@@ -5857,23 +5811,23 @@
       </c>
       <c r="B103" s="121"/>
       <c r="C103" s="115" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="D103" s="123" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="E103" s="82"/>
       <c r="F103" s="87"/>
       <c r="G103" s="87"/>
       <c r="H103" s="82"/>
       <c r="I103" s="83" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="J103" s="83"/>
       <c r="K103" s="83"/>
       <c r="L103" s="82"/>
       <c r="M103" s="81" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="N103" s="82"/>
       <c r="O103" s="82"/>
@@ -5887,23 +5841,23 @@
       <c r="C104" s="115" t="s">
         <v>36</v>
       </c>
-      <c r="D104" s="163" t="s">
-        <v>238</v>
+      <c r="D104" s="147" t="s">
+        <v>237</v>
       </c>
       <c r="E104" s="82"/>
       <c r="F104" s="87"/>
       <c r="G104" s="87"/>
       <c r="H104" s="82"/>
       <c r="I104" s="81" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="J104" s="83" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="K104" s="83"/>
       <c r="L104" s="82"/>
       <c r="M104" s="81" t="s">
-        <v>242</v>
+        <v>474</v>
       </c>
       <c r="N104" s="82"/>
       <c r="O104" s="82"/>
@@ -5918,22 +5872,22 @@
         <v>36</v>
       </c>
       <c r="D105" s="123" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="E105" s="82"/>
       <c r="F105" s="87"/>
       <c r="G105" s="87"/>
       <c r="H105" s="82"/>
       <c r="I105" s="81" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="J105" s="83" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="K105" s="83"/>
       <c r="L105" s="82"/>
       <c r="M105" s="81" t="s">
-        <v>245</v>
+        <v>475</v>
       </c>
       <c r="N105" s="82"/>
       <c r="O105" s="82"/>
@@ -5948,20 +5902,20 @@
         <v>36</v>
       </c>
       <c r="D106" s="123" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="E106" s="82"/>
       <c r="F106" s="87"/>
       <c r="G106" s="87"/>
       <c r="H106" s="82"/>
       <c r="I106" s="81" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="J106" s="83"/>
       <c r="K106" s="83"/>
       <c r="L106" s="82"/>
       <c r="M106" s="81" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="N106" s="82"/>
       <c r="O106" s="82"/>
@@ -5976,28 +5930,28 @@
         <v>36</v>
       </c>
       <c r="D107" s="123" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="E107" s="82"/>
       <c r="F107" s="87" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="G107" s="87"/>
       <c r="H107" s="82"/>
       <c r="I107" s="81" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="J107" s="83"/>
       <c r="K107" s="83"/>
       <c r="L107" s="82"/>
       <c r="M107" s="81" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="N107" s="82"/>
       <c r="O107" s="82"/>
       <c r="P107" s="82"/>
     </row>
-    <row r="108" spans="1:16" ht="102" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:16" ht="51" x14ac:dyDescent="0.2">
       <c r="A108" s="116" t="s">
         <v>16</v>
       </c>
@@ -6009,11 +5963,9 @@
       <c r="G108" s="87"/>
       <c r="H108" s="82"/>
       <c r="I108" s="83" t="s">
-        <v>235</v>
-      </c>
-      <c r="J108" s="83" t="s">
-        <v>253</v>
-      </c>
+        <v>234</v>
+      </c>
+      <c r="J108" s="83"/>
       <c r="K108" s="83"/>
       <c r="L108" s="82"/>
       <c r="M108" s="83"/>
@@ -6026,20 +5978,20 @@
         <v>16</v>
       </c>
       <c r="B109" s="94" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="C109" s="115" t="s">
         <v>36</v>
       </c>
       <c r="D109" s="123" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E109" s="82"/>
       <c r="F109" s="87"/>
       <c r="G109" s="87"/>
       <c r="H109" s="82"/>
       <c r="I109" s="83" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="J109" s="83"/>
       <c r="K109" s="83"/>
@@ -6058,20 +6010,20 @@
         <v>36</v>
       </c>
       <c r="D110" s="123" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="E110" s="82"/>
       <c r="F110" s="87"/>
       <c r="G110" s="87"/>
       <c r="H110" s="82"/>
       <c r="I110" s="81" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="J110" s="83"/>
       <c r="K110" s="81"/>
       <c r="L110" s="87"/>
       <c r="M110" s="81" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="N110" s="82"/>
       <c r="O110" s="82"/>
@@ -6086,28 +6038,28 @@
         <v>36</v>
       </c>
       <c r="D111" s="123" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="E111" s="82"/>
       <c r="F111" s="87" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="G111" s="87"/>
       <c r="H111" s="82"/>
       <c r="I111" s="81" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="J111" s="83"/>
       <c r="K111" s="81"/>
       <c r="L111" s="87"/>
       <c r="M111" s="81" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="N111" s="82"/>
       <c r="O111" s="82"/>
       <c r="P111" s="82"/>
     </row>
-    <row r="112" spans="1:16" ht="34" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:16" ht="17" x14ac:dyDescent="0.2">
       <c r="A112" s="114" t="s">
         <v>26</v>
       </c>
@@ -6116,20 +6068,20 @@
         <v>36</v>
       </c>
       <c r="D112" s="123" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="E112" s="82"/>
       <c r="F112" s="87"/>
       <c r="G112" s="87"/>
       <c r="H112" s="82"/>
       <c r="I112" s="81" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="J112" s="83"/>
       <c r="K112" s="81"/>
       <c r="L112" s="87"/>
       <c r="M112" s="81" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="N112" s="82"/>
       <c r="O112" s="82"/>
@@ -6141,25 +6093,25 @@
       </c>
       <c r="B113" s="121"/>
       <c r="C113" s="115" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="D113" s="123" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="E113" s="82"/>
       <c r="F113" s="93" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G113" s="87"/>
       <c r="H113" s="82"/>
       <c r="I113" s="81" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="J113" s="83"/>
       <c r="K113" s="81"/>
       <c r="L113" s="87"/>
       <c r="M113" s="81" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="N113" s="82"/>
       <c r="O113" s="82"/>
@@ -6170,20 +6122,20 @@
         <v>16</v>
       </c>
       <c r="B114" s="94" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="C114" s="115" t="s">
         <v>36</v>
       </c>
       <c r="D114" s="123" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E114" s="82"/>
       <c r="F114" s="87"/>
       <c r="G114" s="87"/>
       <c r="H114" s="82"/>
       <c r="I114" s="83" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="J114" s="83"/>
       <c r="K114" s="83"/>
@@ -6202,7 +6154,7 @@
         <v>36</v>
       </c>
       <c r="D115" s="123" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="E115" s="82"/>
       <c r="F115" s="87"/>
@@ -6226,20 +6178,20 @@
         <v>36</v>
       </c>
       <c r="D116" s="123" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="E116" s="82"/>
       <c r="F116" s="87"/>
       <c r="G116" s="87"/>
       <c r="H116" s="82"/>
       <c r="I116" s="81" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="J116" s="83"/>
       <c r="K116" s="83"/>
       <c r="L116" s="82"/>
       <c r="M116" s="81" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="N116" s="82"/>
       <c r="O116" s="82"/>
@@ -6254,7 +6206,7 @@
         <v>36</v>
       </c>
       <c r="D117" s="123" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="E117" s="82"/>
       <c r="F117" s="87"/>
@@ -6278,7 +6230,7 @@
         <v>36</v>
       </c>
       <c r="D118" s="123" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="E118" s="82"/>
       <c r="F118" s="87"/>
@@ -6302,33 +6254,33 @@
         <v>36</v>
       </c>
       <c r="D119" s="123" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="E119" s="82"/>
       <c r="F119" s="87" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G119" s="87"/>
       <c r="H119" s="82"/>
       <c r="I119" s="81" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="J119" s="83" t="s">
-        <v>302</v>
+        <v>295</v>
       </c>
       <c r="K119" s="83"/>
       <c r="L119" s="82"/>
       <c r="M119" s="81" t="s">
-        <v>300</v>
+        <v>293</v>
       </c>
       <c r="N119" s="82" t="s">
-        <v>299</v>
+        <v>292</v>
       </c>
       <c r="O119" s="82" t="s">
-        <v>298</v>
+        <v>291</v>
       </c>
       <c r="P119" t="s">
-        <v>301</v>
+        <v>294</v>
       </c>
     </row>
     <row r="120" spans="1:16" ht="17" x14ac:dyDescent="0.2">
@@ -6340,20 +6292,20 @@
         <v>36</v>
       </c>
       <c r="D120" s="123" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="E120" s="82"/>
       <c r="F120" s="87"/>
       <c r="G120" s="87"/>
       <c r="H120" s="82"/>
       <c r="I120" s="81" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="J120" s="83"/>
       <c r="K120" s="83"/>
       <c r="L120" s="82"/>
       <c r="M120" s="81" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="N120" s="82"/>
       <c r="O120" s="82"/>
@@ -6368,17 +6320,17 @@
         <v>36</v>
       </c>
       <c r="D121" s="123" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="E121" s="82"/>
       <c r="F121" s="87"/>
       <c r="G121" s="87"/>
       <c r="H121" s="82"/>
       <c r="I121" s="81" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="J121" s="83" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="K121" s="83"/>
       <c r="L121" s="82"/>
@@ -6396,20 +6348,20 @@
         <v>36</v>
       </c>
       <c r="D122" s="123" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="E122" s="82"/>
       <c r="F122" s="87"/>
       <c r="G122" s="87"/>
       <c r="H122" s="82"/>
       <c r="I122" s="81" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="J122" s="83"/>
       <c r="K122" s="83"/>
       <c r="L122" s="82"/>
       <c r="M122" s="81" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="N122" s="82"/>
       <c r="O122" s="82"/>
@@ -6421,25 +6373,25 @@
       </c>
       <c r="B123" s="121"/>
       <c r="C123" s="115" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="D123" s="123" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="E123" s="82"/>
       <c r="F123" s="93" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G123" s="87"/>
       <c r="H123" s="82"/>
       <c r="I123" s="81" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="J123" s="83"/>
       <c r="K123" s="83"/>
       <c r="L123" s="82"/>
       <c r="M123" s="81" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="N123" s="82"/>
       <c r="O123" s="82"/>
@@ -6454,14 +6406,14 @@
         <v>36</v>
       </c>
       <c r="D124" s="124" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E124" s="82"/>
       <c r="F124" s="87"/>
       <c r="G124" s="87"/>
       <c r="H124" s="82"/>
       <c r="I124" s="81" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="J124" s="83"/>
       <c r="K124" s="83"/>
@@ -6476,20 +6428,20 @@
         <v>16</v>
       </c>
       <c r="B125" s="94" t="s">
-        <v>292</v>
+        <v>286</v>
       </c>
       <c r="C125" s="115" t="s">
         <v>36</v>
       </c>
       <c r="D125" s="123" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E125" s="82"/>
       <c r="F125" s="87"/>
       <c r="G125" s="87"/>
       <c r="H125" s="82"/>
       <c r="I125" s="83" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="J125" s="83"/>
       <c r="K125" s="83"/>
@@ -6505,17 +6457,17 @@
       </c>
       <c r="B126" s="121"/>
       <c r="C126" s="115" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="D126" s="124" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="E126" s="82"/>
       <c r="F126" s="87"/>
       <c r="G126" s="87"/>
       <c r="H126" s="82"/>
       <c r="I126" s="81" t="s">
-        <v>291</v>
+        <v>285</v>
       </c>
       <c r="J126" s="83"/>
       <c r="K126" s="83"/>
@@ -6525,7 +6477,7 @@
       <c r="O126" s="82"/>
       <c r="P126" s="82"/>
     </row>
-    <row r="127" spans="1:16" ht="204" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:16" ht="51" x14ac:dyDescent="0.2">
       <c r="A127" s="114" t="s">
         <v>26</v>
       </c>
@@ -6534,22 +6486,20 @@
         <v>36</v>
       </c>
       <c r="D127" s="125" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="E127" s="82"/>
       <c r="F127" s="87"/>
       <c r="G127" s="87"/>
       <c r="H127" s="82"/>
       <c r="I127" s="81" t="s">
-        <v>296</v>
-      </c>
-      <c r="J127" s="83" t="s">
-        <v>297</v>
-      </c>
+        <v>290</v>
+      </c>
+      <c r="J127" s="83"/>
       <c r="K127" s="83"/>
       <c r="L127" s="82"/>
       <c r="M127" s="81" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="N127" s="82"/>
       <c r="O127" s="82"/>
@@ -6564,20 +6514,20 @@
         <v>36</v>
       </c>
       <c r="D128" s="126" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="E128" s="82"/>
       <c r="F128" s="87"/>
       <c r="G128" s="87"/>
       <c r="H128" s="82"/>
       <c r="I128" s="81" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="J128" s="83"/>
       <c r="K128" s="81"/>
       <c r="L128" s="87"/>
       <c r="M128" s="81" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="N128" s="82"/>
       <c r="O128" s="82"/>
@@ -6592,28 +6542,28 @@
         <v>36</v>
       </c>
       <c r="D129" s="126" t="s">
-        <v>293</v>
+        <v>287</v>
       </c>
       <c r="E129" s="82"/>
       <c r="F129" s="87" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="G129" s="87"/>
       <c r="H129" s="82"/>
       <c r="I129" s="81" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="J129" s="83"/>
       <c r="K129" s="81"/>
       <c r="L129" s="87"/>
       <c r="M129" s="81" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="N129" s="82"/>
       <c r="O129" s="82"/>
       <c r="P129" s="82"/>
     </row>
-    <row r="130" spans="1:16" ht="34" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:16" ht="17" x14ac:dyDescent="0.2">
       <c r="A130" s="114" t="s">
         <v>26</v>
       </c>
@@ -6622,20 +6572,20 @@
         <v>36</v>
       </c>
       <c r="D130" s="123" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="E130" s="82"/>
       <c r="F130" s="87"/>
       <c r="G130" s="87"/>
       <c r="H130" s="82"/>
       <c r="I130" s="81" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="J130" s="83"/>
       <c r="K130" s="81"/>
       <c r="L130" s="87"/>
       <c r="M130" s="81" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="N130" s="82"/>
       <c r="O130" s="82"/>
@@ -6647,25 +6597,25 @@
       </c>
       <c r="B131" s="121"/>
       <c r="C131" s="115" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="D131" s="123" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="E131" s="82"/>
       <c r="F131" s="93" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G131" s="87"/>
       <c r="H131" s="82"/>
       <c r="I131" s="81" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="J131" s="83"/>
       <c r="K131" s="81"/>
       <c r="L131" s="87"/>
       <c r="M131" s="81" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="N131" s="82"/>
       <c r="O131" s="82"/>
@@ -6676,20 +6626,20 @@
         <v>16</v>
       </c>
       <c r="B132" s="94" t="s">
-        <v>303</v>
+        <v>296</v>
       </c>
       <c r="C132" s="115" t="s">
         <v>36</v>
       </c>
       <c r="D132" s="123" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E132" s="82"/>
       <c r="F132" s="87"/>
       <c r="G132" s="87"/>
       <c r="H132" s="82"/>
       <c r="I132" s="83" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="J132" s="83"/>
       <c r="K132" s="83"/>
@@ -6708,7 +6658,7 @@
         <v>36</v>
       </c>
       <c r="D133" s="123" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="E133" s="82"/>
       <c r="F133" s="87"/>
@@ -6732,20 +6682,20 @@
         <v>36</v>
       </c>
       <c r="D134" s="123" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="E134" s="82"/>
       <c r="F134" s="87"/>
       <c r="G134" s="87"/>
       <c r="H134" s="82"/>
       <c r="I134" s="81" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="J134" s="83"/>
       <c r="K134" s="83"/>
       <c r="L134" s="82"/>
       <c r="M134" s="81" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="N134" s="82"/>
       <c r="O134" s="82"/>
@@ -6760,7 +6710,7 @@
         <v>36</v>
       </c>
       <c r="D135" s="123" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="E135" s="82"/>
       <c r="F135" s="87"/>
@@ -6784,7 +6734,7 @@
         <v>36</v>
       </c>
       <c r="D136" s="123" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="E136" s="82"/>
       <c r="F136" s="87"/>
@@ -6808,14 +6758,14 @@
         <v>36</v>
       </c>
       <c r="D137" s="123" t="s">
-        <v>307</v>
+        <v>300</v>
       </c>
       <c r="E137" s="82"/>
       <c r="F137" s="87"/>
       <c r="G137" s="87"/>
       <c r="H137" s="82"/>
       <c r="I137" s="81" t="s">
-        <v>306</v>
+        <v>299</v>
       </c>
       <c r="J137" s="83"/>
       <c r="K137" s="83"/>
@@ -6834,14 +6784,14 @@
         <v>36</v>
       </c>
       <c r="D138" s="123" t="s">
-        <v>305</v>
+        <v>298</v>
       </c>
       <c r="E138" s="82"/>
       <c r="F138" s="87"/>
       <c r="G138" s="87"/>
       <c r="H138" s="82"/>
       <c r="I138" s="122" t="s">
-        <v>316</v>
+        <v>309</v>
       </c>
       <c r="J138" s="83"/>
       <c r="K138" s="83"/>
@@ -6860,33 +6810,33 @@
         <v>36</v>
       </c>
       <c r="D139" s="123" t="s">
-        <v>304</v>
+        <v>297</v>
       </c>
       <c r="E139" s="82"/>
       <c r="F139" s="87" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G139" s="87"/>
       <c r="H139" s="82"/>
       <c r="I139" s="81" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="J139" s="83" t="s">
-        <v>302</v>
+        <v>295</v>
       </c>
       <c r="K139" s="83"/>
       <c r="L139" s="82"/>
       <c r="M139" s="81" t="s">
-        <v>300</v>
+        <v>293</v>
       </c>
       <c r="N139" s="82" t="s">
-        <v>299</v>
+        <v>292</v>
       </c>
       <c r="O139" s="82" t="s">
-        <v>298</v>
+        <v>291</v>
       </c>
       <c r="P139" t="s">
-        <v>301</v>
+        <v>294</v>
       </c>
     </row>
     <row r="140" spans="1:16" ht="17" x14ac:dyDescent="0.2">
@@ -6898,20 +6848,20 @@
         <v>36</v>
       </c>
       <c r="D140" s="123" t="s">
-        <v>311</v>
+        <v>304</v>
       </c>
       <c r="E140" s="82"/>
       <c r="F140" s="87"/>
       <c r="G140" s="87"/>
       <c r="H140" s="82"/>
       <c r="I140" s="81" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="J140" s="83"/>
       <c r="K140" s="83"/>
       <c r="L140" s="82"/>
       <c r="M140" s="81" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="N140" s="82"/>
       <c r="O140" s="82"/>
@@ -6926,17 +6876,17 @@
         <v>36</v>
       </c>
       <c r="D141" s="123" t="s">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="E141" s="82"/>
       <c r="F141" s="87"/>
       <c r="G141" s="87"/>
       <c r="H141" s="82"/>
       <c r="I141" s="81" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="J141" s="83" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="K141" s="83"/>
       <c r="L141" s="82"/>
@@ -6946,22 +6896,22 @@
       <c r="P141" s="82"/>
     </row>
     <row r="142" spans="1:16" ht="34" x14ac:dyDescent="0.2">
-      <c r="A142" s="114" t="s">
-        <v>26</v>
+      <c r="A142" s="116" t="s">
+        <v>16</v>
       </c>
       <c r="B142" s="121"/>
       <c r="C142" s="115" t="s">
-        <v>308</v>
+        <v>301</v>
       </c>
       <c r="D142" s="123" t="s">
-        <v>305</v>
+        <v>298</v>
       </c>
       <c r="E142" s="82"/>
       <c r="F142" s="87"/>
       <c r="G142" s="87"/>
       <c r="H142" s="82"/>
       <c r="I142" s="81" t="s">
-        <v>309</v>
+        <v>302</v>
       </c>
       <c r="J142" s="83"/>
       <c r="K142" s="83"/>
@@ -6971,7 +6921,7 @@
       <c r="O142" s="82"/>
       <c r="P142" s="82"/>
     </row>
-    <row r="143" spans="1:16" ht="204" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:16" ht="51" x14ac:dyDescent="0.2">
       <c r="A143" s="114" t="s">
         <v>26</v>
       </c>
@@ -6980,22 +6930,20 @@
         <v>36</v>
       </c>
       <c r="D143" s="123" t="s">
-        <v>313</v>
+        <v>306</v>
       </c>
       <c r="E143" s="82"/>
       <c r="F143" s="87"/>
       <c r="G143" s="87"/>
       <c r="H143" s="82"/>
       <c r="I143" s="81" t="s">
-        <v>310</v>
-      </c>
-      <c r="J143" s="83" t="s">
-        <v>297</v>
-      </c>
+        <v>303</v>
+      </c>
+      <c r="J143" s="83"/>
       <c r="K143" s="83"/>
       <c r="L143" s="82"/>
       <c r="M143" s="81" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="N143" s="82"/>
       <c r="O143" s="82"/>
@@ -7010,20 +6958,20 @@
         <v>36</v>
       </c>
       <c r="D144" s="123" t="s">
-        <v>314</v>
+        <v>307</v>
       </c>
       <c r="E144" s="82"/>
       <c r="F144" s="87"/>
       <c r="G144" s="87"/>
       <c r="H144" s="82"/>
       <c r="I144" s="81" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="J144" s="83"/>
       <c r="K144" s="81"/>
       <c r="L144" s="87"/>
       <c r="M144" s="81" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="N144" s="82"/>
       <c r="O144" s="82"/>
@@ -7038,22 +6986,22 @@
         <v>36</v>
       </c>
       <c r="D145" s="123" t="s">
-        <v>317</v>
+        <v>310</v>
       </c>
       <c r="E145" s="82"/>
       <c r="F145" s="87" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="G145" s="87"/>
       <c r="H145" s="82"/>
       <c r="I145" s="81" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="J145" s="83"/>
       <c r="K145" s="81"/>
       <c r="L145" s="87"/>
       <c r="M145" s="81" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="N145" s="82"/>
       <c r="O145" s="82"/>
@@ -7068,20 +7016,20 @@
         <v>36</v>
       </c>
       <c r="D146" s="123" t="s">
-        <v>315</v>
+        <v>308</v>
       </c>
       <c r="E146" s="82"/>
       <c r="F146" s="87"/>
       <c r="G146" s="87"/>
       <c r="H146" s="82"/>
       <c r="I146" s="81" t="s">
-        <v>318</v>
+        <v>311</v>
       </c>
       <c r="J146" s="83"/>
       <c r="K146" s="81"/>
       <c r="L146" s="87"/>
       <c r="M146" s="81" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="N146" s="82"/>
       <c r="O146" s="82"/>
@@ -7093,25 +7041,25 @@
       </c>
       <c r="B147" s="121"/>
       <c r="C147" s="115" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="D147" s="123" t="s">
-        <v>320</v>
+        <v>313</v>
       </c>
       <c r="E147" s="82"/>
       <c r="F147" s="93" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G147" s="87"/>
       <c r="H147" s="82"/>
       <c r="I147" s="81" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="J147" s="83"/>
       <c r="K147" s="83"/>
       <c r="L147" s="82"/>
       <c r="M147" s="81" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="N147" s="82"/>
       <c r="O147" s="82"/>
@@ -7126,7 +7074,7 @@
         <v>36</v>
       </c>
       <c r="D148" s="123" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="E148" s="82"/>
       <c r="F148" s="87"/>
@@ -7150,7 +7098,7 @@
         <v>36</v>
       </c>
       <c r="D149" s="123" t="s">
-        <v>322</v>
+        <v>315</v>
       </c>
       <c r="E149" s="82"/>
       <c r="F149" s="87"/>
@@ -7174,7 +7122,7 @@
         <v>36</v>
       </c>
       <c r="D150" s="123" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="E150" s="82"/>
       <c r="F150" s="87"/>
@@ -7198,14 +7146,14 @@
         <v>36</v>
       </c>
       <c r="D151" s="123" t="s">
-        <v>324</v>
+        <v>317</v>
       </c>
       <c r="E151" s="82"/>
       <c r="F151" s="87"/>
       <c r="G151" s="87"/>
       <c r="H151" s="82"/>
       <c r="I151" s="81" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="J151" s="83"/>
       <c r="K151" s="83"/>
@@ -7217,7 +7165,7 @@
     </row>
     <row r="152" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A152" s="67" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B152" s="64"/>
       <c r="C152" s="64"/>
@@ -7241,10 +7189,10 @@
       </c>
       <c r="B153" s="60"/>
       <c r="C153" s="62" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D153" s="128" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E153" s="82"/>
       <c r="F153" s="87"/>
@@ -7268,7 +7216,7 @@
         <v>36</v>
       </c>
       <c r="D154" s="123" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E154" s="82"/>
       <c r="F154" s="87"/>
@@ -7292,7 +7240,7 @@
         <v>36</v>
       </c>
       <c r="D155" s="123" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E155" s="82"/>
       <c r="F155" s="87"/>
@@ -7318,7 +7266,7 @@
         <v>36</v>
       </c>
       <c r="D156" s="124" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="E156" s="82"/>
       <c r="F156" s="87"/>
@@ -7342,24 +7290,24 @@
         <v>36</v>
       </c>
       <c r="D157" s="123" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E157" s="82"/>
       <c r="F157" s="87" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="G157" s="87" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="H157" s="82"/>
       <c r="I157" s="81" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="J157" s="83"/>
       <c r="K157" s="83"/>
       <c r="L157" s="82"/>
       <c r="M157" s="96" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="N157" s="18"/>
       <c r="O157" s="18"/>
@@ -7371,23 +7319,23 @@
       </c>
       <c r="B158" s="63"/>
       <c r="C158" s="62" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D158" s="123" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E158" s="82"/>
       <c r="F158" s="87"/>
       <c r="G158" s="87"/>
       <c r="H158" s="82"/>
       <c r="I158" s="81" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="J158" s="83"/>
       <c r="K158" s="83"/>
       <c r="L158" s="82"/>
       <c r="M158" s="96" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="N158" s="18"/>
       <c r="O158" s="18"/>
@@ -7395,7 +7343,7 @@
     </row>
     <row r="159" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A159" s="67" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B159" s="64"/>
       <c r="C159" s="64"/>
@@ -7422,7 +7370,7 @@
         <v>36</v>
       </c>
       <c r="D160" s="123" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E160" s="82"/>
       <c r="F160" s="87"/>
@@ -7446,20 +7394,20 @@
         <v>36</v>
       </c>
       <c r="D161" s="130" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E161" s="82"/>
       <c r="F161" s="87"/>
       <c r="G161" s="87"/>
       <c r="H161" s="132"/>
       <c r="I161" s="124" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="J161" s="110"/>
       <c r="K161" s="83"/>
       <c r="L161" s="98"/>
       <c r="M161" s="81" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="N161" s="18"/>
       <c r="O161" s="18"/>
@@ -7470,11 +7418,11 @@
         <v>26</v>
       </c>
       <c r="B167" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C167" s="136"/>
       <c r="D167" s="135" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E167" s="77" t="s">
         <v>14</v>
@@ -7484,7 +7432,7 @@
       <c r="H167" s="78"/>
       <c r="I167" s="79"/>
       <c r="J167" s="79" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="K167" s="79"/>
       <c r="L167" s="80"/>
@@ -7502,7 +7450,7 @@
         <v>36</v>
       </c>
       <c r="D168" s="84" t="s">
-        <v>355</v>
+        <v>347</v>
       </c>
       <c r="E168" s="82"/>
       <c r="F168" s="82"/>
@@ -7526,7 +7474,7 @@
         <v>36</v>
       </c>
       <c r="D169" s="92" t="s">
-        <v>356</v>
+        <v>348</v>
       </c>
       <c r="E169" s="82"/>
       <c r="F169" s="82"/>
@@ -7552,7 +7500,7 @@
         <v>36</v>
       </c>
       <c r="D170" s="86" t="s">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="E170" s="82"/>
       <c r="F170" s="82"/>
@@ -7572,13 +7520,13 @@
         <v>16</v>
       </c>
       <c r="B171" s="94" t="s">
+        <v>331</v>
+      </c>
+      <c r="C171" s="83" t="s">
+        <v>36</v>
+      </c>
+      <c r="D171" s="86" t="s">
         <v>339</v>
-      </c>
-      <c r="C171" s="83" t="s">
-        <v>36</v>
-      </c>
-      <c r="D171" s="86" t="s">
-        <v>347</v>
       </c>
       <c r="E171" s="82"/>
       <c r="F171" s="82"/>
@@ -7598,13 +7546,13 @@
         <v>16</v>
       </c>
       <c r="B172" s="94" t="s">
-        <v>340</v>
+        <v>332</v>
       </c>
       <c r="C172" s="83" t="s">
         <v>36</v>
       </c>
       <c r="D172" s="86" t="s">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="E172" s="82"/>
       <c r="F172" s="87"/>
@@ -7624,13 +7572,13 @@
         <v>16</v>
       </c>
       <c r="B173" s="94" t="s">
-        <v>341</v>
+        <v>333</v>
       </c>
       <c r="C173" s="83" t="s">
         <v>36</v>
       </c>
       <c r="D173" s="86" t="s">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="E173" s="82"/>
       <c r="F173" s="87"/>
@@ -7650,13 +7598,13 @@
         <v>16</v>
       </c>
       <c r="B174" s="94" t="s">
-        <v>342</v>
+        <v>334</v>
       </c>
       <c r="C174" s="83" t="s">
         <v>36</v>
       </c>
       <c r="D174" s="86" t="s">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="E174" s="82"/>
       <c r="F174" s="87"/>
@@ -7676,20 +7624,20 @@
         <v>16</v>
       </c>
       <c r="B175" s="94" t="s">
-        <v>343</v>
+        <v>335</v>
       </c>
       <c r="C175" s="83" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="D175" s="86" t="s">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="E175" s="82"/>
       <c r="F175" s="87"/>
       <c r="G175" s="87"/>
       <c r="H175" s="82"/>
       <c r="I175" s="81" t="s">
-        <v>345</v>
+        <v>337</v>
       </c>
       <c r="J175" s="83"/>
       <c r="K175" s="83"/>
@@ -7704,20 +7652,20 @@
         <v>16</v>
       </c>
       <c r="B176" s="94" t="s">
-        <v>344</v>
+        <v>336</v>
       </c>
       <c r="C176" s="83" t="s">
         <v>36</v>
       </c>
       <c r="D176" s="86" t="s">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="E176" s="82"/>
       <c r="F176" s="87"/>
       <c r="G176" s="87"/>
       <c r="H176" s="82"/>
       <c r="I176" s="81" t="s">
-        <v>346</v>
+        <v>338</v>
       </c>
       <c r="J176" s="83"/>
       <c r="K176" s="83"/>
@@ -7736,7 +7684,7 @@
         <v>36</v>
       </c>
       <c r="D177" s="85" t="s">
-        <v>348</v>
+        <v>340</v>
       </c>
       <c r="E177" s="82"/>
       <c r="F177" s="87"/>
@@ -7760,20 +7708,20 @@
         <v>36</v>
       </c>
       <c r="D178" s="81" t="s">
-        <v>357</v>
+        <v>349</v>
       </c>
       <c r="E178" s="82"/>
       <c r="F178" s="87"/>
       <c r="G178" s="87"/>
       <c r="H178" s="82"/>
       <c r="I178" s="81" t="s">
-        <v>359</v>
+        <v>351</v>
       </c>
       <c r="J178" s="83"/>
       <c r="K178" s="83"/>
       <c r="L178" s="82"/>
       <c r="M178" s="85" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="N178" s="82"/>
       <c r="O178" s="82"/>
@@ -7785,23 +7733,23 @@
       </c>
       <c r="B179" s="83"/>
       <c r="C179" s="83" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D179" s="81" t="s">
-        <v>358</v>
+        <v>350</v>
       </c>
       <c r="E179" s="82"/>
       <c r="F179" s="87"/>
       <c r="G179" s="87"/>
       <c r="H179" s="82"/>
       <c r="I179" s="81" t="s">
-        <v>360</v>
+        <v>352</v>
       </c>
       <c r="J179" s="83"/>
       <c r="K179" s="83"/>
       <c r="L179" s="82"/>
       <c r="M179" s="85" t="s">
-        <v>375</v>
+        <v>367</v>
       </c>
       <c r="N179" s="82"/>
       <c r="O179" s="82"/>
@@ -7816,14 +7764,14 @@
         <v>36</v>
       </c>
       <c r="D180" s="139" t="s">
-        <v>361</v>
+        <v>353</v>
       </c>
       <c r="E180" s="82"/>
       <c r="F180" s="109"/>
       <c r="G180" s="87"/>
       <c r="H180" s="81"/>
       <c r="I180" s="121" t="s">
-        <v>362</v>
+        <v>354</v>
       </c>
       <c r="J180" s="94"/>
       <c r="K180" s="94"/>
@@ -7842,14 +7790,14 @@
         <v>18</v>
       </c>
       <c r="D181" s="81" t="s">
-        <v>363</v>
+        <v>355</v>
       </c>
       <c r="E181" s="82"/>
       <c r="F181" s="87"/>
       <c r="G181" s="87"/>
       <c r="H181" s="82"/>
       <c r="I181" s="81" t="s">
-        <v>364</v>
+        <v>356</v>
       </c>
       <c r="J181" s="83"/>
       <c r="K181" s="83"/>
@@ -7865,23 +7813,23 @@
       </c>
       <c r="B182" s="121"/>
       <c r="C182" s="115" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="D182" s="123" t="s">
-        <v>365</v>
+        <v>357</v>
       </c>
       <c r="E182" s="82"/>
       <c r="F182" s="87"/>
       <c r="G182" s="87"/>
       <c r="H182" s="82"/>
       <c r="I182" s="83" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="J182" s="83"/>
       <c r="K182" s="83"/>
       <c r="L182" s="82"/>
       <c r="M182" s="81" t="s">
-        <v>370</v>
+        <v>362</v>
       </c>
       <c r="N182" s="82"/>
       <c r="O182" s="82"/>
@@ -7896,22 +7844,22 @@
         <v>36</v>
       </c>
       <c r="D183" s="123" t="s">
-        <v>366</v>
+        <v>358</v>
       </c>
       <c r="E183" s="82"/>
       <c r="F183" s="87"/>
       <c r="G183" s="87"/>
       <c r="H183" s="82"/>
       <c r="I183" s="81" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="J183" s="83" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="K183" s="83"/>
       <c r="L183" s="82"/>
       <c r="M183" s="81" t="s">
-        <v>371</v>
+        <v>363</v>
       </c>
       <c r="N183" s="82"/>
       <c r="O183" s="82"/>
@@ -7926,22 +7874,22 @@
         <v>36</v>
       </c>
       <c r="D184" s="123" t="s">
-        <v>367</v>
+        <v>359</v>
       </c>
       <c r="E184" s="82"/>
       <c r="F184" s="87"/>
       <c r="G184" s="87"/>
       <c r="H184" s="82"/>
       <c r="I184" s="81" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="J184" s="83" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="K184" s="83"/>
       <c r="L184" s="82"/>
       <c r="M184" s="81" t="s">
-        <v>372</v>
+        <v>364</v>
       </c>
       <c r="N184" s="82"/>
       <c r="O184" s="82"/>
@@ -7956,20 +7904,20 @@
         <v>36</v>
       </c>
       <c r="D185" s="123" t="s">
-        <v>368</v>
+        <v>360</v>
       </c>
       <c r="E185" s="82"/>
       <c r="F185" s="87"/>
       <c r="G185" s="87"/>
       <c r="H185" s="82"/>
       <c r="I185" s="81" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="J185" s="83"/>
       <c r="K185" s="83"/>
       <c r="L185" s="82"/>
       <c r="M185" s="81" t="s">
-        <v>373</v>
+        <v>365</v>
       </c>
       <c r="N185" s="82"/>
       <c r="O185" s="82"/>
@@ -7984,22 +7932,22 @@
         <v>36</v>
       </c>
       <c r="D186" s="123" t="s">
-        <v>369</v>
+        <v>361</v>
       </c>
       <c r="E186" s="82"/>
       <c r="F186" s="87" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="G186" s="87"/>
       <c r="H186" s="82"/>
       <c r="I186" s="81" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="J186" s="83"/>
       <c r="K186" s="83"/>
       <c r="L186" s="82"/>
       <c r="M186" s="81" t="s">
-        <v>374</v>
+        <v>366</v>
       </c>
       <c r="N186" s="82"/>
       <c r="O186" s="82"/>
@@ -8014,22 +7962,22 @@
         <v>36</v>
       </c>
       <c r="D187" s="123" t="s">
-        <v>385</v>
+        <v>377</v>
       </c>
       <c r="E187" s="82"/>
       <c r="F187" s="87"/>
       <c r="G187" s="87"/>
       <c r="H187" s="82"/>
       <c r="I187" s="81" t="s">
-        <v>383</v>
+        <v>375</v>
       </c>
       <c r="J187" s="83" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="K187" s="83"/>
       <c r="L187" s="82"/>
       <c r="M187" s="81" t="s">
-        <v>384</v>
+        <v>376</v>
       </c>
       <c r="N187" s="82"/>
       <c r="O187" s="82"/>
@@ -8041,23 +7989,23 @@
       </c>
       <c r="B188" s="121"/>
       <c r="C188" s="115" t="s">
+        <v>95</v>
+      </c>
+      <c r="D188" s="123" t="s">
         <v>96</v>
-      </c>
-      <c r="D188" s="123" t="s">
-        <v>97</v>
       </c>
       <c r="E188" s="82"/>
       <c r="F188" s="87"/>
       <c r="G188" s="87"/>
       <c r="H188" s="82"/>
       <c r="I188" s="81" t="s">
-        <v>391</v>
+        <v>383</v>
       </c>
       <c r="J188" s="83"/>
       <c r="K188" s="83"/>
       <c r="L188" s="82"/>
       <c r="M188" s="81" t="s">
-        <v>392</v>
+        <v>384</v>
       </c>
       <c r="N188" s="82"/>
       <c r="O188" s="82"/>
@@ -8072,11 +8020,11 @@
         <v>36</v>
       </c>
       <c r="D189" s="123" t="s">
-        <v>386</v>
+        <v>378</v>
       </c>
       <c r="E189" s="82"/>
       <c r="F189" s="87" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G189" s="87"/>
       <c r="H189" s="82"/>
@@ -8085,7 +8033,7 @@
       <c r="K189" s="83"/>
       <c r="L189" s="82"/>
       <c r="M189" s="81" t="s">
-        <v>393</v>
+        <v>385</v>
       </c>
       <c r="N189" s="82"/>
       <c r="O189" s="82"/>
@@ -8100,7 +8048,7 @@
         <v>36</v>
       </c>
       <c r="D190" s="123" t="s">
-        <v>387</v>
+        <v>379</v>
       </c>
       <c r="E190" s="82"/>
       <c r="F190" s="87"/>
@@ -8111,7 +8059,7 @@
       <c r="K190" s="83"/>
       <c r="L190" s="82"/>
       <c r="M190" s="81" t="s">
-        <v>394</v>
+        <v>386</v>
       </c>
       <c r="N190" s="82"/>
       <c r="O190" s="82"/>
@@ -8126,7 +8074,7 @@
         <v>36</v>
       </c>
       <c r="D191" s="123" t="s">
-        <v>389</v>
+        <v>381</v>
       </c>
       <c r="E191" s="82"/>
       <c r="F191" s="87"/>
@@ -8137,7 +8085,7 @@
       <c r="K191" s="83"/>
       <c r="L191" s="82"/>
       <c r="M191" s="81" t="s">
-        <v>395</v>
+        <v>387</v>
       </c>
       <c r="N191" s="82"/>
       <c r="O191" s="82"/>
@@ -8152,7 +8100,7 @@
         <v>36</v>
       </c>
       <c r="D192" s="123" t="s">
-        <v>388</v>
+        <v>380</v>
       </c>
       <c r="E192" s="82"/>
       <c r="F192" s="87"/>
@@ -8173,22 +8121,22 @@
       </c>
       <c r="B193" s="146"/>
       <c r="C193" s="95" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D193" s="123" t="s">
-        <v>390</v>
+        <v>382</v>
       </c>
       <c r="I193" s="123"/>
       <c r="J193" s="144"/>
       <c r="K193" s="123"/>
       <c r="L193" s="141"/>
       <c r="M193" s="123" t="s">
-        <v>396</v>
+        <v>388</v>
       </c>
     </row>
     <row r="194" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A194" s="67" t="s">
-        <v>382</v>
+        <v>374</v>
       </c>
       <c r="B194" s="64"/>
       <c r="C194" s="64"/>
@@ -8206,7 +8154,7 @@
       <c r="O194" s="18"/>
       <c r="P194" s="18"/>
     </row>
-    <row r="195" spans="1:16" ht="102" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:16" ht="51" x14ac:dyDescent="0.2">
       <c r="A195" s="116" t="s">
         <v>16</v>
       </c>
@@ -8218,11 +8166,9 @@
       <c r="G195" s="87"/>
       <c r="H195" s="82"/>
       <c r="I195" s="83" t="s">
-        <v>235</v>
-      </c>
-      <c r="J195" s="83" t="s">
-        <v>253</v>
-      </c>
+        <v>234</v>
+      </c>
+      <c r="J195" s="83"/>
       <c r="K195" s="83"/>
       <c r="L195" s="82"/>
       <c r="M195" s="83"/>
@@ -8235,20 +8181,20 @@
         <v>16</v>
       </c>
       <c r="B196" s="94" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="C196" s="115" t="s">
         <v>36</v>
       </c>
       <c r="D196" s="123" t="s">
-        <v>365</v>
+        <v>357</v>
       </c>
       <c r="E196" s="82"/>
       <c r="F196" s="87"/>
       <c r="G196" s="87"/>
       <c r="H196" s="82"/>
       <c r="I196" s="83" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="J196" s="83"/>
       <c r="K196" s="83"/>
@@ -8267,20 +8213,20 @@
         <v>36</v>
       </c>
       <c r="D197" s="123" t="s">
-        <v>397</v>
+        <v>389</v>
       </c>
       <c r="E197" s="82"/>
       <c r="F197" s="87"/>
       <c r="G197" s="87"/>
       <c r="H197" s="82"/>
       <c r="I197" s="81" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="J197" s="83"/>
       <c r="K197" s="81"/>
       <c r="L197" s="87"/>
       <c r="M197" s="81" t="s">
-        <v>373</v>
+        <v>365</v>
       </c>
       <c r="N197" s="82"/>
       <c r="O197" s="82"/>
@@ -8295,22 +8241,22 @@
         <v>36</v>
       </c>
       <c r="D198" s="123" t="s">
-        <v>398</v>
+        <v>390</v>
       </c>
       <c r="E198" s="82"/>
       <c r="F198" s="87" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="G198" s="87"/>
       <c r="H198" s="82"/>
       <c r="I198" s="81" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="J198" s="83"/>
       <c r="K198" s="81"/>
       <c r="L198" s="87"/>
       <c r="M198" s="81" t="s">
-        <v>374</v>
+        <v>366</v>
       </c>
       <c r="N198" s="82"/>
       <c r="O198" s="82"/>
@@ -8325,20 +8271,20 @@
         <v>36</v>
       </c>
       <c r="D199" s="123" t="s">
-        <v>442</v>
+        <v>434</v>
       </c>
       <c r="E199" s="82"/>
       <c r="F199" s="87"/>
       <c r="G199" s="87"/>
       <c r="H199" s="82"/>
       <c r="I199" s="81" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="J199" s="83"/>
       <c r="K199" s="81"/>
       <c r="L199" s="87"/>
       <c r="M199" s="81" t="s">
-        <v>376</v>
+        <v>368</v>
       </c>
       <c r="N199" s="82"/>
       <c r="O199" s="82"/>
@@ -8350,25 +8296,25 @@
       </c>
       <c r="B200" s="121"/>
       <c r="C200" s="115" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="D200" s="123" t="s">
-        <v>443</v>
+        <v>435</v>
       </c>
       <c r="E200" s="82"/>
       <c r="F200" s="93" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G200" s="87"/>
       <c r="H200" s="82"/>
       <c r="I200" s="81" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="J200" s="83"/>
       <c r="K200" s="81"/>
       <c r="L200" s="87"/>
       <c r="M200" s="81" t="s">
-        <v>377</v>
+        <v>369</v>
       </c>
       <c r="N200" s="82"/>
       <c r="O200" s="82"/>
@@ -8379,20 +8325,20 @@
         <v>16</v>
       </c>
       <c r="B201" s="94" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="C201" s="115" t="s">
         <v>36</v>
       </c>
       <c r="D201" s="123" t="s">
-        <v>444</v>
+        <v>436</v>
       </c>
       <c r="E201" s="82"/>
       <c r="F201" s="87"/>
       <c r="G201" s="87"/>
       <c r="H201" s="82"/>
       <c r="I201" s="83" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="J201" s="83"/>
       <c r="K201" s="83"/>
@@ -8411,7 +8357,7 @@
         <v>36</v>
       </c>
       <c r="D202" s="123" t="s">
-        <v>401</v>
+        <v>393</v>
       </c>
       <c r="E202" s="82"/>
       <c r="F202" s="87"/>
@@ -8435,20 +8381,20 @@
         <v>36</v>
       </c>
       <c r="D203" s="123" t="s">
-        <v>402</v>
+        <v>394</v>
       </c>
       <c r="E203" s="82"/>
       <c r="F203" s="87"/>
       <c r="G203" s="87"/>
       <c r="H203" s="82"/>
       <c r="I203" s="81" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="J203" s="83"/>
       <c r="K203" s="83"/>
       <c r="L203" s="82"/>
       <c r="M203" s="81" t="s">
-        <v>378</v>
+        <v>370</v>
       </c>
       <c r="N203" s="82"/>
       <c r="O203" s="82"/>
@@ -8463,7 +8409,7 @@
         <v>36</v>
       </c>
       <c r="D204" s="123" t="s">
-        <v>403</v>
+        <v>395</v>
       </c>
       <c r="E204" s="82"/>
       <c r="F204" s="87"/>
@@ -8487,7 +8433,7 @@
         <v>36</v>
       </c>
       <c r="D205" s="123" t="s">
-        <v>404</v>
+        <v>396</v>
       </c>
       <c r="E205" s="82"/>
       <c r="F205" s="87"/>
@@ -8511,33 +8457,33 @@
         <v>36</v>
       </c>
       <c r="D206" s="123" t="s">
-        <v>405</v>
+        <v>397</v>
       </c>
       <c r="E206" s="82"/>
       <c r="F206" s="87" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G206" s="87"/>
       <c r="H206" s="82"/>
       <c r="I206" s="81" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="J206" s="83" t="s">
-        <v>302</v>
+        <v>295</v>
       </c>
       <c r="K206" s="83"/>
       <c r="L206" s="82"/>
       <c r="M206" s="81" t="s">
-        <v>379</v>
+        <v>371</v>
       </c>
       <c r="N206" s="82" t="s">
-        <v>299</v>
+        <v>292</v>
       </c>
       <c r="O206" s="82" t="s">
-        <v>298</v>
+        <v>291</v>
       </c>
       <c r="P206" t="s">
-        <v>301</v>
+        <v>294</v>
       </c>
     </row>
     <row r="207" spans="1:16" ht="17" x14ac:dyDescent="0.2">
@@ -8549,20 +8495,20 @@
         <v>36</v>
       </c>
       <c r="D207" s="123" t="s">
-        <v>445</v>
+        <v>437</v>
       </c>
       <c r="E207" s="82"/>
       <c r="F207" s="87"/>
       <c r="G207" s="87"/>
       <c r="H207" s="82"/>
       <c r="I207" s="81" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="J207" s="83"/>
       <c r="K207" s="83"/>
       <c r="L207" s="82"/>
       <c r="M207" s="81" t="s">
-        <v>380</v>
+        <v>372</v>
       </c>
       <c r="N207" s="82"/>
       <c r="O207" s="82"/>
@@ -8577,17 +8523,17 @@
         <v>36</v>
       </c>
       <c r="D208" s="123" t="s">
-        <v>446</v>
+        <v>438</v>
       </c>
       <c r="E208" s="82"/>
       <c r="F208" s="87"/>
       <c r="G208" s="87"/>
       <c r="H208" s="82"/>
       <c r="I208" s="81" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="J208" s="83" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="K208" s="83"/>
       <c r="L208" s="82"/>
@@ -8605,20 +8551,20 @@
         <v>36</v>
       </c>
       <c r="D209" s="123" t="s">
-        <v>447</v>
+        <v>439</v>
       </c>
       <c r="E209" s="82"/>
       <c r="F209" s="87"/>
       <c r="G209" s="87"/>
       <c r="H209" s="82"/>
       <c r="I209" s="81" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="J209" s="83"/>
       <c r="K209" s="83"/>
       <c r="L209" s="82"/>
       <c r="M209" s="81" t="s">
-        <v>376</v>
+        <v>368</v>
       </c>
       <c r="N209" s="82"/>
       <c r="O209" s="82"/>
@@ -8630,25 +8576,25 @@
       </c>
       <c r="B210" s="121"/>
       <c r="C210" s="115" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="D210" s="123" t="s">
-        <v>448</v>
+        <v>440</v>
       </c>
       <c r="E210" s="82"/>
       <c r="F210" s="93" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G210" s="87"/>
       <c r="H210" s="82"/>
       <c r="I210" s="81" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="J210" s="83"/>
       <c r="K210" s="83"/>
       <c r="L210" s="82"/>
       <c r="M210" s="81" t="s">
-        <v>377</v>
+        <v>369</v>
       </c>
       <c r="N210" s="82"/>
       <c r="O210" s="82"/>
@@ -8663,14 +8609,14 @@
         <v>36</v>
       </c>
       <c r="D211" s="124" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="E211" s="82"/>
       <c r="F211" s="87"/>
       <c r="G211" s="87"/>
       <c r="H211" s="82"/>
       <c r="I211" s="81" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="J211" s="83"/>
       <c r="K211" s="83"/>
@@ -8685,20 +8631,20 @@
         <v>16</v>
       </c>
       <c r="B212" s="94" t="s">
-        <v>292</v>
+        <v>286</v>
       </c>
       <c r="C212" s="115" t="s">
         <v>36</v>
       </c>
       <c r="D212" s="123" t="s">
-        <v>365</v>
+        <v>357</v>
       </c>
       <c r="E212" s="82"/>
       <c r="F212" s="87"/>
       <c r="G212" s="87"/>
       <c r="H212" s="82"/>
       <c r="I212" s="83" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="J212" s="83"/>
       <c r="K212" s="83"/>
@@ -8714,17 +8660,17 @@
       </c>
       <c r="B213" s="121"/>
       <c r="C213" s="115" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="D213" s="124" t="s">
-        <v>406</v>
+        <v>398</v>
       </c>
       <c r="E213" s="82"/>
       <c r="F213" s="87"/>
       <c r="G213" s="87"/>
       <c r="H213" s="82"/>
       <c r="I213" s="81" t="s">
-        <v>291</v>
+        <v>285</v>
       </c>
       <c r="J213" s="83"/>
       <c r="K213" s="83"/>
@@ -8734,7 +8680,7 @@
       <c r="O213" s="82"/>
       <c r="P213" s="82"/>
     </row>
-    <row r="214" spans="1:16" ht="204" x14ac:dyDescent="0.2">
+    <row r="214" spans="1:16" ht="51" x14ac:dyDescent="0.2">
       <c r="A214" s="114" t="s">
         <v>26</v>
       </c>
@@ -8743,22 +8689,20 @@
         <v>36</v>
       </c>
       <c r="D214" s="125" t="s">
-        <v>407</v>
+        <v>399</v>
       </c>
       <c r="E214" s="82"/>
       <c r="F214" s="87"/>
       <c r="G214" s="87"/>
       <c r="H214" s="82"/>
       <c r="I214" s="81" t="s">
-        <v>296</v>
-      </c>
-      <c r="J214" s="83" t="s">
-        <v>297</v>
-      </c>
+        <v>290</v>
+      </c>
+      <c r="J214" s="83"/>
       <c r="K214" s="83"/>
       <c r="L214" s="82"/>
       <c r="M214" s="81" t="s">
-        <v>381</v>
+        <v>373</v>
       </c>
       <c r="N214" s="82"/>
       <c r="O214" s="82"/>
@@ -8773,20 +8717,20 @@
         <v>36</v>
       </c>
       <c r="D215" s="126" t="s">
-        <v>408</v>
+        <v>400</v>
       </c>
       <c r="E215" s="82"/>
       <c r="F215" s="87"/>
       <c r="G215" s="87"/>
       <c r="H215" s="82"/>
       <c r="I215" s="81" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="J215" s="83"/>
       <c r="K215" s="81"/>
       <c r="L215" s="87"/>
       <c r="M215" s="81" t="s">
-        <v>373</v>
+        <v>365</v>
       </c>
       <c r="N215" s="82"/>
       <c r="O215" s="82"/>
@@ -8801,22 +8745,22 @@
         <v>36</v>
       </c>
       <c r="D216" s="126" t="s">
-        <v>409</v>
+        <v>401</v>
       </c>
       <c r="E216" s="82"/>
       <c r="F216" s="87" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="G216" s="87"/>
       <c r="H216" s="82"/>
       <c r="I216" s="81" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="J216" s="83"/>
       <c r="K216" s="81"/>
       <c r="L216" s="87"/>
       <c r="M216" s="81" t="s">
-        <v>374</v>
+        <v>366</v>
       </c>
       <c r="N216" s="82"/>
       <c r="O216" s="82"/>
@@ -8831,20 +8775,20 @@
         <v>36</v>
       </c>
       <c r="D217" s="123" t="s">
-        <v>399</v>
+        <v>391</v>
       </c>
       <c r="E217" s="82"/>
       <c r="F217" s="87"/>
       <c r="G217" s="87"/>
       <c r="H217" s="82"/>
       <c r="I217" s="81" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="J217" s="83"/>
       <c r="K217" s="81"/>
       <c r="L217" s="87"/>
       <c r="M217" s="81" t="s">
-        <v>376</v>
+        <v>368</v>
       </c>
       <c r="N217" s="82"/>
       <c r="O217" s="82"/>
@@ -8856,25 +8800,25 @@
       </c>
       <c r="B218" s="121"/>
       <c r="C218" s="115" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="D218" s="123" t="s">
-        <v>400</v>
+        <v>392</v>
       </c>
       <c r="E218" s="82"/>
       <c r="F218" s="93" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G218" s="87"/>
       <c r="H218" s="82"/>
       <c r="I218" s="81" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="J218" s="83"/>
       <c r="K218" s="81"/>
       <c r="L218" s="87"/>
       <c r="M218" s="81" t="s">
-        <v>377</v>
+        <v>369</v>
       </c>
       <c r="N218" s="82"/>
       <c r="O218" s="82"/>
@@ -8885,20 +8829,20 @@
         <v>16</v>
       </c>
       <c r="B219" s="94" t="s">
-        <v>303</v>
+        <v>296</v>
       </c>
       <c r="C219" s="115" t="s">
         <v>36</v>
       </c>
       <c r="D219" s="123" t="s">
-        <v>444</v>
+        <v>436</v>
       </c>
       <c r="E219" s="82"/>
       <c r="F219" s="87"/>
       <c r="G219" s="87"/>
       <c r="H219" s="82"/>
       <c r="I219" s="83" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="J219" s="83"/>
       <c r="K219" s="83"/>
@@ -8917,7 +8861,7 @@
         <v>36</v>
       </c>
       <c r="D220" s="123" t="s">
-        <v>401</v>
+        <v>393</v>
       </c>
       <c r="E220" s="82"/>
       <c r="F220" s="87"/>
@@ -8941,20 +8885,20 @@
         <v>36</v>
       </c>
       <c r="D221" s="123" t="s">
-        <v>402</v>
+        <v>394</v>
       </c>
       <c r="E221" s="82"/>
       <c r="F221" s="87"/>
       <c r="G221" s="87"/>
       <c r="H221" s="82"/>
       <c r="I221" s="81" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="J221" s="83"/>
       <c r="K221" s="83"/>
       <c r="L221" s="82"/>
       <c r="M221" s="81" t="s">
-        <v>378</v>
+        <v>370</v>
       </c>
       <c r="N221" s="82"/>
       <c r="O221" s="82"/>
@@ -8969,7 +8913,7 @@
         <v>36</v>
       </c>
       <c r="D222" s="123" t="s">
-        <v>403</v>
+        <v>395</v>
       </c>
       <c r="E222" s="82"/>
       <c r="F222" s="87"/>
@@ -8993,7 +8937,7 @@
         <v>36</v>
       </c>
       <c r="D223" s="123" t="s">
-        <v>404</v>
+        <v>396</v>
       </c>
       <c r="E223" s="82"/>
       <c r="F223" s="87"/>
@@ -9017,14 +8961,14 @@
         <v>36</v>
       </c>
       <c r="D224" s="123" t="s">
-        <v>410</v>
+        <v>402</v>
       </c>
       <c r="E224" s="82"/>
       <c r="F224" s="87"/>
       <c r="G224" s="87"/>
       <c r="H224" s="82"/>
       <c r="I224" s="81" t="s">
-        <v>306</v>
+        <v>299</v>
       </c>
       <c r="J224" s="83"/>
       <c r="K224" s="83"/>
@@ -9043,14 +8987,14 @@
         <v>36</v>
       </c>
       <c r="D225" s="123" t="s">
-        <v>411</v>
+        <v>403</v>
       </c>
       <c r="E225" s="82"/>
       <c r="F225" s="87"/>
       <c r="G225" s="87"/>
       <c r="H225" s="82"/>
       <c r="I225" s="122" t="s">
-        <v>316</v>
+        <v>309</v>
       </c>
       <c r="J225" s="83"/>
       <c r="K225" s="83"/>
@@ -9069,33 +9013,33 @@
         <v>36</v>
       </c>
       <c r="D226" s="123" t="s">
-        <v>412</v>
+        <v>404</v>
       </c>
       <c r="E226" s="82"/>
       <c r="F226" s="87" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G226" s="87"/>
       <c r="H226" s="82"/>
       <c r="I226" s="81" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="J226" s="83" t="s">
-        <v>302</v>
+        <v>295</v>
       </c>
       <c r="K226" s="83"/>
       <c r="L226" s="82"/>
       <c r="M226" s="81" t="s">
-        <v>379</v>
+        <v>371</v>
       </c>
       <c r="N226" s="82" t="s">
-        <v>299</v>
+        <v>292</v>
       </c>
       <c r="O226" s="82" t="s">
-        <v>298</v>
+        <v>291</v>
       </c>
       <c r="P226" t="s">
-        <v>301</v>
+        <v>294</v>
       </c>
     </row>
     <row r="227" spans="1:16" ht="17" x14ac:dyDescent="0.2">
@@ -9107,20 +9051,20 @@
         <v>36</v>
       </c>
       <c r="D227" s="123" t="s">
-        <v>413</v>
+        <v>405</v>
       </c>
       <c r="E227" s="82"/>
       <c r="F227" s="87"/>
       <c r="G227" s="87"/>
       <c r="H227" s="82"/>
       <c r="I227" s="81" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="J227" s="83"/>
       <c r="K227" s="83"/>
       <c r="L227" s="82"/>
       <c r="M227" s="81" t="s">
-        <v>380</v>
+        <v>372</v>
       </c>
       <c r="N227" s="82"/>
       <c r="O227" s="82"/>
@@ -9135,17 +9079,17 @@
         <v>36</v>
       </c>
       <c r="D228" s="123" t="s">
-        <v>414</v>
+        <v>406</v>
       </c>
       <c r="E228" s="82"/>
       <c r="F228" s="87"/>
       <c r="G228" s="87"/>
       <c r="H228" s="82"/>
       <c r="I228" s="81" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="J228" s="83" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="K228" s="83"/>
       <c r="L228" s="82"/>
@@ -9160,17 +9104,17 @@
       </c>
       <c r="B229" s="121"/>
       <c r="C229" s="115" t="s">
-        <v>308</v>
+        <v>301</v>
       </c>
       <c r="D229" s="123" t="s">
-        <v>411</v>
+        <v>403</v>
       </c>
       <c r="E229" s="82"/>
       <c r="F229" s="87"/>
       <c r="G229" s="87"/>
       <c r="H229" s="82"/>
       <c r="I229" s="81" t="s">
-        <v>309</v>
+        <v>302</v>
       </c>
       <c r="J229" s="83"/>
       <c r="K229" s="83"/>
@@ -9180,7 +9124,7 @@
       <c r="O229" s="82"/>
       <c r="P229" s="82"/>
     </row>
-    <row r="230" spans="1:16" ht="204" x14ac:dyDescent="0.2">
+    <row r="230" spans="1:16" ht="51" x14ac:dyDescent="0.2">
       <c r="A230" s="114" t="s">
         <v>26</v>
       </c>
@@ -9189,22 +9133,20 @@
         <v>36</v>
       </c>
       <c r="D230" s="123" t="s">
-        <v>415</v>
+        <v>407</v>
       </c>
       <c r="E230" s="82"/>
       <c r="F230" s="87"/>
       <c r="G230" s="87"/>
       <c r="H230" s="82"/>
       <c r="I230" s="81" t="s">
-        <v>310</v>
-      </c>
-      <c r="J230" s="83" t="s">
-        <v>297</v>
-      </c>
+        <v>303</v>
+      </c>
+      <c r="J230" s="83"/>
       <c r="K230" s="83"/>
       <c r="L230" s="82"/>
       <c r="M230" s="81" t="s">
-        <v>381</v>
+        <v>373</v>
       </c>
       <c r="N230" s="82"/>
       <c r="O230" s="82"/>
@@ -9219,20 +9161,20 @@
         <v>36</v>
       </c>
       <c r="D231" s="123" t="s">
-        <v>416</v>
+        <v>408</v>
       </c>
       <c r="E231" s="82"/>
       <c r="F231" s="87"/>
       <c r="G231" s="87"/>
       <c r="H231" s="82"/>
       <c r="I231" s="81" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="J231" s="83"/>
       <c r="K231" s="81"/>
       <c r="L231" s="87"/>
       <c r="M231" s="81" t="s">
-        <v>373</v>
+        <v>365</v>
       </c>
       <c r="N231" s="82"/>
       <c r="O231" s="82"/>
@@ -9247,22 +9189,22 @@
         <v>36</v>
       </c>
       <c r="D232" s="123" t="s">
-        <v>417</v>
+        <v>409</v>
       </c>
       <c r="E232" s="82"/>
       <c r="F232" s="87" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="G232" s="87"/>
       <c r="H232" s="82"/>
       <c r="I232" s="81" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="J232" s="83"/>
       <c r="K232" s="81"/>
       <c r="L232" s="87"/>
       <c r="M232" s="81" t="s">
-        <v>374</v>
+        <v>366</v>
       </c>
       <c r="N232" s="82"/>
       <c r="O232" s="82"/>
@@ -9277,20 +9219,20 @@
         <v>36</v>
       </c>
       <c r="D233" s="123" t="s">
-        <v>418</v>
+        <v>410</v>
       </c>
       <c r="E233" s="82"/>
       <c r="F233" s="87"/>
       <c r="G233" s="87"/>
       <c r="H233" s="82"/>
       <c r="I233" s="81" t="s">
-        <v>318</v>
+        <v>311</v>
       </c>
       <c r="J233" s="83"/>
       <c r="K233" s="81"/>
       <c r="L233" s="87"/>
       <c r="M233" s="81" t="s">
-        <v>376</v>
+        <v>368</v>
       </c>
       <c r="N233" s="82"/>
       <c r="O233" s="82"/>
@@ -9302,25 +9244,25 @@
       </c>
       <c r="B234" s="121"/>
       <c r="C234" s="115" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="D234" s="123" t="s">
-        <v>419</v>
+        <v>411</v>
       </c>
       <c r="E234" s="82"/>
       <c r="F234" s="93" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G234" s="87"/>
       <c r="H234" s="82"/>
       <c r="I234" s="81" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="J234" s="83"/>
       <c r="K234" s="83"/>
       <c r="L234" s="82"/>
       <c r="M234" s="81" t="s">
-        <v>377</v>
+        <v>369</v>
       </c>
       <c r="N234" s="82"/>
       <c r="O234" s="82"/>
@@ -9335,7 +9277,7 @@
         <v>36</v>
       </c>
       <c r="D235" s="123" t="s">
-        <v>420</v>
+        <v>412</v>
       </c>
       <c r="E235" s="82"/>
       <c r="F235" s="87"/>
@@ -9359,7 +9301,7 @@
         <v>36</v>
       </c>
       <c r="D236" s="123" t="s">
-        <v>421</v>
+        <v>413</v>
       </c>
       <c r="E236" s="82"/>
       <c r="F236" s="87"/>
@@ -9383,7 +9325,7 @@
         <v>36</v>
       </c>
       <c r="D237" s="123" t="s">
-        <v>422</v>
+        <v>414</v>
       </c>
       <c r="E237" s="82"/>
       <c r="F237" s="87"/>
@@ -9407,14 +9349,14 @@
         <v>36</v>
       </c>
       <c r="D238" s="123" t="s">
-        <v>423</v>
+        <v>415</v>
       </c>
       <c r="E238" s="82"/>
       <c r="F238" s="87"/>
       <c r="G238" s="87"/>
       <c r="H238" s="82"/>
       <c r="I238" s="81" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="J238" s="83"/>
       <c r="K238" s="83"/>
@@ -9425,21 +9367,21 @@
       <c r="P238" s="18"/>
     </row>
     <row r="239" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A239" s="153" t="s">
-        <v>451</v>
-      </c>
-      <c r="B239" s="153"/>
-      <c r="C239" s="153"/>
-      <c r="D239" s="154"/>
-      <c r="E239" s="154"/>
-      <c r="F239" s="154"/>
-      <c r="G239" s="154"/>
-      <c r="H239" s="153"/>
-      <c r="I239" s="155"/>
-      <c r="J239" s="153"/>
-      <c r="K239" s="153"/>
-      <c r="L239" s="153"/>
-      <c r="M239" s="153"/>
+      <c r="A239" s="154" t="s">
+        <v>443</v>
+      </c>
+      <c r="B239" s="154"/>
+      <c r="C239" s="154"/>
+      <c r="D239" s="155"/>
+      <c r="E239" s="155"/>
+      <c r="F239" s="155"/>
+      <c r="G239" s="155"/>
+      <c r="H239" s="154"/>
+      <c r="I239" s="156"/>
+      <c r="J239" s="154"/>
+      <c r="K239" s="154"/>
+      <c r="L239" s="154"/>
+      <c r="M239" s="154"/>
       <c r="N239" s="82"/>
       <c r="O239" s="82"/>
       <c r="P239" s="82"/>
@@ -9449,13 +9391,13 @@
         <v>26</v>
       </c>
       <c r="B240" s="83" t="s">
-        <v>449</v>
+        <v>441</v>
       </c>
       <c r="C240" s="115" t="s">
         <v>36</v>
       </c>
       <c r="D240" s="81" t="s">
-        <v>468</v>
+        <v>460</v>
       </c>
       <c r="E240" s="82"/>
       <c r="F240" s="87"/>
@@ -9466,26 +9408,26 @@
       <c r="K240" s="83"/>
       <c r="L240" s="83"/>
       <c r="M240" s="81" t="s">
-        <v>450</v>
+        <v>442</v>
       </c>
       <c r="N240" s="82"/>
       <c r="O240" s="82"/>
       <c r="P240" s="82"/>
     </row>
     <row r="241" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A241" s="150" t="s">
-        <v>452</v>
-      </c>
-      <c r="B241" s="151"/>
-      <c r="C241" s="151"/>
-      <c r="D241" s="151"/>
-      <c r="E241" s="151"/>
-      <c r="F241" s="151"/>
-      <c r="G241" s="151"/>
-      <c r="H241" s="151"/>
-      <c r="I241" s="151"/>
-      <c r="J241" s="151"/>
-      <c r="K241" s="152"/>
+      <c r="A241" s="151" t="s">
+        <v>444</v>
+      </c>
+      <c r="B241" s="152"/>
+      <c r="C241" s="152"/>
+      <c r="D241" s="152"/>
+      <c r="E241" s="152"/>
+      <c r="F241" s="152"/>
+      <c r="G241" s="152"/>
+      <c r="H241" s="152"/>
+      <c r="I241" s="152"/>
+      <c r="J241" s="152"/>
+      <c r="K241" s="153"/>
       <c r="L241" s="100"/>
       <c r="M241" s="100"/>
       <c r="N241" s="82"/>
@@ -9497,45 +9439,45 @@
         <v>26</v>
       </c>
       <c r="B242" s="83" t="s">
-        <v>453</v>
+        <v>445</v>
       </c>
       <c r="C242" s="115" t="s">
         <v>36</v>
       </c>
       <c r="D242" s="81" t="s">
-        <v>469</v>
+        <v>461</v>
       </c>
       <c r="E242" s="82"/>
       <c r="F242" s="87"/>
       <c r="G242" s="87"/>
       <c r="H242" s="94"/>
       <c r="I242" s="81" t="s">
-        <v>454</v>
+        <v>446</v>
       </c>
       <c r="J242" s="83"/>
       <c r="K242" s="83"/>
       <c r="L242" s="83"/>
       <c r="M242" s="81" t="s">
-        <v>455</v>
+        <v>447</v>
       </c>
       <c r="N242" s="82"/>
       <c r="O242" s="82"/>
       <c r="P242" s="82"/>
     </row>
     <row r="243" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A243" s="150" t="s">
-        <v>458</v>
-      </c>
-      <c r="B243" s="156"/>
-      <c r="C243" s="151"/>
-      <c r="D243" s="151"/>
-      <c r="E243" s="151"/>
-      <c r="F243" s="151"/>
-      <c r="G243" s="151"/>
-      <c r="H243" s="151"/>
-      <c r="I243" s="156"/>
-      <c r="J243" s="156"/>
-      <c r="K243" s="157"/>
+      <c r="A243" s="151" t="s">
+        <v>450</v>
+      </c>
+      <c r="B243" s="157"/>
+      <c r="C243" s="152"/>
+      <c r="D243" s="152"/>
+      <c r="E243" s="152"/>
+      <c r="F243" s="152"/>
+      <c r="G243" s="152"/>
+      <c r="H243" s="152"/>
+      <c r="I243" s="157"/>
+      <c r="J243" s="157"/>
+      <c r="K243" s="158"/>
       <c r="L243" s="140"/>
       <c r="M243" s="140"/>
       <c r="N243" s="82"/>
@@ -9551,7 +9493,7 @@
         <v>36</v>
       </c>
       <c r="D244" s="123" t="s">
-        <v>401</v>
+        <v>393</v>
       </c>
       <c r="I244" s="123"/>
       <c r="J244" s="144"/>
@@ -9568,7 +9510,7 @@
         <v>36</v>
       </c>
       <c r="D245" s="123" t="s">
-        <v>459</v>
+        <v>451</v>
       </c>
       <c r="I245" s="123"/>
       <c r="J245" s="144"/>
@@ -9585,7 +9527,7 @@
         <v>36</v>
       </c>
       <c r="D246" s="123" t="s">
-        <v>460</v>
+        <v>452</v>
       </c>
       <c r="I246" s="123"/>
       <c r="J246" s="144"/>
@@ -9602,7 +9544,7 @@
         <v>36</v>
       </c>
       <c r="D247" s="123" t="s">
-        <v>461</v>
+        <v>453</v>
       </c>
       <c r="I247" s="123"/>
       <c r="J247" s="144"/>
@@ -9619,23 +9561,23 @@
         <v>36</v>
       </c>
       <c r="D248" s="123" t="s">
-        <v>462</v>
+        <v>454</v>
       </c>
       <c r="I248" s="123" t="s">
         <v>45</v>
       </c>
       <c r="J248" s="144" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="K248" s="123"/>
       <c r="L248" s="141"/>
       <c r="M248" s="123" t="s">
-        <v>463</v>
+        <v>455</v>
       </c>
     </row>
     <row r="249" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A249" s="120" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B249" s="102"/>
       <c r="C249" s="102"/>
@@ -9645,10 +9587,10 @@
       <c r="G249" s="103"/>
       <c r="H249" s="103"/>
       <c r="I249" s="102"/>
-      <c r="J249" s="147"/>
-      <c r="K249" s="147"/>
-      <c r="L249" s="148"/>
-      <c r="M249" s="149"/>
+      <c r="J249" s="148"/>
+      <c r="K249" s="148"/>
+      <c r="L249" s="149"/>
+      <c r="M249" s="150"/>
       <c r="N249" s="82"/>
       <c r="O249" s="82"/>
       <c r="P249" s="82"/>
@@ -9658,13 +9600,13 @@
         <v>26</v>
       </c>
       <c r="B250" s="83" t="s">
-        <v>464</v>
+        <v>456</v>
       </c>
       <c r="C250" s="115" t="s">
         <v>36</v>
       </c>
       <c r="D250" s="81" t="s">
-        <v>444</v>
+        <v>436</v>
       </c>
       <c r="E250" s="82"/>
       <c r="F250" s="87"/>
@@ -9675,7 +9617,7 @@
       <c r="K250" s="83"/>
       <c r="L250" s="83"/>
       <c r="M250" s="81" t="s">
-        <v>471</v>
+        <v>463</v>
       </c>
       <c r="N250" s="82"/>
       <c r="O250" s="82"/>
@@ -9683,7 +9625,7 @@
     </row>
     <row r="251" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A251" s="120" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B251" s="102"/>
       <c r="C251" s="102"/>
@@ -9693,10 +9635,10 @@
       <c r="G251" s="103"/>
       <c r="H251" s="103"/>
       <c r="I251" s="102"/>
-      <c r="J251" s="147"/>
-      <c r="K251" s="147"/>
-      <c r="L251" s="148"/>
-      <c r="M251" s="149"/>
+      <c r="J251" s="148"/>
+      <c r="K251" s="148"/>
+      <c r="L251" s="149"/>
+      <c r="M251" s="150"/>
       <c r="N251" s="82"/>
       <c r="O251" s="82"/>
       <c r="P251" s="82"/>
@@ -9706,13 +9648,13 @@
         <v>26</v>
       </c>
       <c r="B252" s="83" t="s">
-        <v>465</v>
+        <v>457</v>
       </c>
       <c r="C252" s="115" t="s">
         <v>36</v>
       </c>
       <c r="D252" s="81" t="s">
-        <v>444</v>
+        <v>436</v>
       </c>
       <c r="E252" s="82"/>
       <c r="F252" s="87"/>
@@ -9723,7 +9665,7 @@
       <c r="K252" s="83"/>
       <c r="L252" s="83"/>
       <c r="M252" s="81" t="s">
-        <v>472</v>
+        <v>464</v>
       </c>
       <c r="N252" s="82"/>
       <c r="O252" s="82"/>
@@ -9731,7 +9673,7 @@
     </row>
     <row r="253" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A253" s="67" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B253" s="64"/>
       <c r="C253" s="64"/>
@@ -9754,13 +9696,13 @@
         <v>26</v>
       </c>
       <c r="B254" s="83" t="s">
-        <v>466</v>
+        <v>458</v>
       </c>
       <c r="C254" s="115" t="s">
         <v>36</v>
       </c>
       <c r="D254" s="81" t="s">
-        <v>444</v>
+        <v>436</v>
       </c>
       <c r="E254" s="82"/>
       <c r="F254" s="87"/>
@@ -9771,7 +9713,7 @@
       <c r="K254" s="83"/>
       <c r="L254" s="83"/>
       <c r="M254" s="81" t="s">
-        <v>473</v>
+        <v>465</v>
       </c>
       <c r="N254" s="82"/>
       <c r="O254" s="82"/>
@@ -9779,7 +9721,7 @@
     </row>
     <row r="255" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A255" s="67" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B255" s="64"/>
       <c r="C255" s="64"/>
@@ -9802,13 +9744,13 @@
         <v>26</v>
       </c>
       <c r="B256" s="83" t="s">
-        <v>467</v>
+        <v>459</v>
       </c>
       <c r="C256" s="115" t="s">
         <v>36</v>
       </c>
       <c r="D256" s="81" t="s">
-        <v>470</v>
+        <v>462</v>
       </c>
       <c r="E256" s="82"/>
       <c r="F256" s="87"/>
@@ -9819,7 +9761,7 @@
       <c r="K256" s="83"/>
       <c r="L256" s="83"/>
       <c r="M256" s="81" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="N256" s="82"/>
       <c r="O256" s="82"/>
@@ -9839,7 +9781,7 @@
     <mergeCell ref="A243:K243"/>
     <mergeCell ref="J249:M249"/>
   </mergeCells>
-  <conditionalFormatting sqref="A58:A60 A62:A78 A80:A96 A98:A151 A153:A158 A181:A193 A195:A248 A250 A252 A254 A256:A1048576 A1:A56">
+  <conditionalFormatting sqref="A1:A56 A58:A60 A62:A78 A80:A96 A98:A151 A153:A158 A181:A193 A195:A248 A250 A252 A254 A256:A1048576">
     <cfRule type="cellIs" dxfId="10" priority="17" operator="equal">
       <formula>"wird nicht gemapped"</formula>
     </cfRule>
@@ -9896,19 +9838,19 @@
     <row r="1" spans="1:26" ht="20" x14ac:dyDescent="0.2">
       <c r="A1" s="26"/>
       <c r="B1" s="27"/>
-      <c r="C1" s="161" t="s">
-        <v>106</v>
-      </c>
-      <c r="D1" s="161"/>
-      <c r="E1" s="162"/>
-      <c r="F1" s="162"/>
+      <c r="C1" s="162" t="s">
+        <v>105</v>
+      </c>
+      <c r="D1" s="162"/>
+      <c r="E1" s="163"/>
+      <c r="F1" s="163"/>
       <c r="I1" s="26"/>
       <c r="J1" s="28"/>
       <c r="K1" s="28"/>
       <c r="L1" s="28"/>
       <c r="M1" s="29"/>
       <c r="N1" s="28" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="O1" s="28"/>
       <c r="P1" s="28"/>
@@ -9929,10 +9871,10 @@
         <v>32</v>
       </c>
       <c r="C2" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>108</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>109</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>2</v>
@@ -9961,7 +9903,7 @@
         <v>9</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="P2" s="2" t="s">
         <v>4</v>
@@ -9985,14 +9927,14 @@
         <v>11</v>
       </c>
       <c r="C3" s="36" t="s">
+        <v>110</v>
+      </c>
+      <c r="D3" s="37" t="s">
         <v>111</v>
-      </c>
-      <c r="D3" s="37" t="s">
-        <v>112</v>
       </c>
       <c r="E3" s="37"/>
       <c r="F3" s="38" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="G3" s="39"/>
       <c r="H3" s="39"/>
@@ -10002,7 +9944,7 @@
       <c r="L3" s="37"/>
       <c r="M3" s="41"/>
       <c r="N3" s="36" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="O3" s="42"/>
       <c r="P3" s="42"/>
@@ -10024,38 +9966,38 @@
       </c>
       <c r="C4" s="45"/>
       <c r="D4" s="45" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E4" s="45" t="s">
+        <v>114</v>
+      </c>
+      <c r="F4" s="46" t="s">
         <v>115</v>
       </c>
-      <c r="F4" s="46" t="s">
+      <c r="G4" s="47" t="s">
         <v>116</v>
       </c>
-      <c r="G4" s="47" t="s">
+      <c r="H4" s="47" t="s">
         <v>117</v>
-      </c>
-      <c r="H4" s="47" t="s">
-        <v>118</v>
       </c>
       <c r="I4" s="40"/>
       <c r="J4" s="6"/>
       <c r="K4" s="6"/>
       <c r="L4" s="6" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="M4" s="41"/>
       <c r="N4" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="O4" s="18" t="s">
         <v>120</v>
       </c>
-      <c r="O4" s="18" t="s">
+      <c r="P4" s="15" t="s">
         <v>121</v>
       </c>
-      <c r="P4" s="15" t="s">
+      <c r="Q4" s="15" t="s">
         <v>122</v>
-      </c>
-      <c r="Q4" s="15" t="s">
-        <v>123</v>
       </c>
       <c r="R4" s="43"/>
       <c r="S4" s="44"/>
@@ -10073,16 +10015,16 @@
         <v>26</v>
       </c>
       <c r="C5" s="45" t="s">
+        <v>123</v>
+      </c>
+      <c r="D5" s="45" t="s">
+        <v>111</v>
+      </c>
+      <c r="E5" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="D5" s="45" t="s">
-        <v>112</v>
-      </c>
-      <c r="E5" s="6" t="s">
+      <c r="F5" s="48" t="s">
         <v>125</v>
-      </c>
-      <c r="F5" s="48" t="s">
-        <v>126</v>
       </c>
       <c r="G5" s="49"/>
       <c r="H5" s="49"/>
@@ -10092,7 +10034,7 @@
       <c r="L5" s="45"/>
       <c r="M5" s="41"/>
       <c r="N5" s="6" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="O5" s="15"/>
       <c r="P5" s="15"/>
@@ -10113,16 +10055,16 @@
         <v>26</v>
       </c>
       <c r="C6" s="45" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D6" s="45" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E6" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="F6" s="48" t="s">
         <v>128</v>
-      </c>
-      <c r="F6" s="48" t="s">
-        <v>129</v>
       </c>
       <c r="G6" s="49"/>
       <c r="H6" s="49"/>
@@ -10132,7 +10074,7 @@
       <c r="L6" s="45"/>
       <c r="M6" s="41"/>
       <c r="N6" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="O6" s="15"/>
       <c r="P6" s="15"/>
@@ -10154,13 +10096,13 @@
       </c>
       <c r="C7" s="45"/>
       <c r="D7" s="45" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E7" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="F7" s="46" t="s">
         <v>131</v>
-      </c>
-      <c r="F7" s="46" t="s">
-        <v>132</v>
       </c>
       <c r="G7" s="47"/>
       <c r="H7" s="47"/>
@@ -10170,7 +10112,7 @@
       <c r="L7" s="45"/>
       <c r="M7" s="41"/>
       <c r="N7" s="6" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="O7" s="15"/>
       <c r="P7" s="15"/>
@@ -10192,13 +10134,13 @@
       </c>
       <c r="C8" s="45"/>
       <c r="D8" s="45" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F8" s="46" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G8" s="47"/>
       <c r="H8" s="47"/>
@@ -10208,7 +10150,7 @@
       <c r="L8" s="45"/>
       <c r="M8" s="41"/>
       <c r="N8" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="O8" s="15"/>
       <c r="P8" s="15"/>
@@ -10230,13 +10172,13 @@
       </c>
       <c r="C9" s="45"/>
       <c r="D9" s="45" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F9" s="46" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="G9" s="47"/>
       <c r="H9" s="47"/>
@@ -10246,7 +10188,7 @@
       <c r="L9" s="45"/>
       <c r="M9" s="41"/>
       <c r="N9" s="6" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="O9" s="15"/>
       <c r="P9" s="15"/>
@@ -10268,36 +10210,36 @@
       </c>
       <c r="C10" s="45"/>
       <c r="D10" s="45" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F10" s="46" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="G10" s="47"/>
       <c r="H10" s="47"/>
       <c r="I10" s="40"/>
       <c r="J10" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="K10" s="6"/>
       <c r="L10" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="M10" s="41"/>
       <c r="N10" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="O10" s="50" t="s">
         <v>141</v>
       </c>
-      <c r="O10" s="50" t="s">
+      <c r="P10" s="15" t="s">
         <v>142</v>
       </c>
-      <c r="P10" s="15" t="s">
+      <c r="Q10" s="15" t="s">
         <v>143</v>
-      </c>
-      <c r="Q10" s="15" t="s">
-        <v>144</v>
       </c>
       <c r="R10" s="43"/>
       <c r="S10" s="44"/>
@@ -10316,25 +10258,25 @@
       </c>
       <c r="C11" s="45"/>
       <c r="D11" s="45" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F11" s="46" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G11" s="47"/>
       <c r="H11" s="47"/>
       <c r="I11" s="40"/>
       <c r="J11" s="6" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="K11" s="6"/>
       <c r="L11" s="6"/>
       <c r="M11" s="41"/>
       <c r="N11" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="O11" s="15"/>
       <c r="P11" s="15"/>
@@ -10355,10 +10297,10 @@
         <v>11</v>
       </c>
       <c r="C12" s="51" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D12" s="51" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E12" s="51"/>
       <c r="F12" s="51"/>
@@ -10370,7 +10312,7 @@
       <c r="L12" s="51"/>
       <c r="M12" s="53"/>
       <c r="N12" s="51" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="O12" s="52"/>
       <c r="P12" s="52"/>
@@ -10392,10 +10334,10 @@
       </c>
       <c r="C13" s="45"/>
       <c r="D13" s="45" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F13" s="46" t="s">
         <v>23</v>
@@ -10408,7 +10350,7 @@
       <c r="L13" s="45"/>
       <c r="M13" s="41"/>
       <c r="N13" s="6" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="O13" s="15"/>
       <c r="P13" s="15"/>
@@ -10430,13 +10372,13 @@
       </c>
       <c r="C14" s="45"/>
       <c r="D14" s="45" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F14" s="46" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G14" s="47"/>
       <c r="H14" s="47"/>
@@ -10446,7 +10388,7 @@
       <c r="L14" s="45"/>
       <c r="M14" s="41"/>
       <c r="N14" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="O14" s="15"/>
       <c r="P14" s="15"/>
@@ -10468,38 +10410,38 @@
       </c>
       <c r="C15" s="45"/>
       <c r="D15" s="45" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E15" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="F15" s="46" t="s">
         <v>154</v>
       </c>
-      <c r="F15" s="46" t="s">
+      <c r="G15" s="25" t="s">
         <v>155</v>
       </c>
-      <c r="G15" s="25" t="s">
+      <c r="H15" s="25" t="s">
         <v>156</v>
-      </c>
-      <c r="H15" s="25" t="s">
-        <v>157</v>
       </c>
       <c r="I15" s="40"/>
       <c r="J15" s="45"/>
       <c r="K15" s="45"/>
       <c r="L15" s="6" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="M15" s="41"/>
       <c r="N15" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="O15" s="54" t="s">
         <v>158</v>
       </c>
-      <c r="O15" s="54" t="s">
+      <c r="P15" s="25" t="s">
         <v>159</v>
       </c>
-      <c r="P15" s="25" t="s">
+      <c r="Q15" s="25" t="s">
         <v>160</v>
-      </c>
-      <c r="Q15" s="25" t="s">
-        <v>161</v>
       </c>
       <c r="R15" s="43"/>
       <c r="S15" s="44"/>
@@ -10518,25 +10460,25 @@
       </c>
       <c r="C16" s="45"/>
       <c r="D16" s="45" t="s">
+        <v>111</v>
+      </c>
+      <c r="E16" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="F16" s="46" t="s">
         <v>112</v>
-      </c>
-      <c r="E16" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="F16" s="46" t="s">
-        <v>113</v>
       </c>
       <c r="G16" s="47"/>
       <c r="H16" s="47"/>
       <c r="I16" s="40"/>
       <c r="J16" s="25" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="K16" s="15"/>
       <c r="L16" s="45"/>
       <c r="M16" s="41"/>
       <c r="N16" s="6" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="O16" s="15"/>
       <c r="P16" s="15"/>
@@ -10557,14 +10499,14 @@
         <v>11</v>
       </c>
       <c r="C17" s="51" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D17" s="51" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E17" s="51"/>
       <c r="F17" s="51" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="G17" s="52"/>
       <c r="H17" s="52"/>
@@ -10574,7 +10516,7 @@
       <c r="L17" s="51"/>
       <c r="M17" s="53"/>
       <c r="N17" s="51" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="O17" s="52"/>
       <c r="P17" s="52"/>
@@ -10596,10 +10538,10 @@
       </c>
       <c r="C18" s="45"/>
       <c r="D18" s="45" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="F18" s="46" t="s">
         <v>23</v>
@@ -10608,13 +10550,13 @@
       <c r="H18" s="47"/>
       <c r="I18" s="40"/>
       <c r="J18" s="25" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="K18" s="6"/>
       <c r="L18" s="45"/>
       <c r="M18" s="41"/>
       <c r="N18" s="6" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="O18" s="15"/>
       <c r="P18" s="15"/>
@@ -10636,10 +10578,10 @@
       </c>
       <c r="C19" s="45"/>
       <c r="D19" s="6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="F19" s="46" t="s">
         <v>27</v>
@@ -10648,22 +10590,22 @@
       <c r="H19" s="47"/>
       <c r="I19" s="40"/>
       <c r="J19" s="6" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="K19" s="6"/>
       <c r="L19" s="6"/>
       <c r="M19" s="41"/>
       <c r="N19" s="6" t="s">
+        <v>170</v>
+      </c>
+      <c r="O19" s="18" t="s">
         <v>171</v>
       </c>
-      <c r="O19" s="18" t="s">
+      <c r="P19" s="55" t="s">
         <v>172</v>
       </c>
-      <c r="P19" s="55" t="s">
+      <c r="Q19" s="17" t="s">
         <v>173</v>
-      </c>
-      <c r="Q19" s="17" t="s">
-        <v>174</v>
       </c>
       <c r="R19" s="43"/>
       <c r="S19" s="44"/>
@@ -10682,25 +10624,25 @@
       </c>
       <c r="C20" s="45"/>
       <c r="D20" s="45" t="s">
+        <v>111</v>
+      </c>
+      <c r="E20" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="F20" s="46" t="s">
         <v>112</v>
-      </c>
-      <c r="E20" s="6" t="s">
-        <v>167</v>
-      </c>
-      <c r="F20" s="46" t="s">
-        <v>113</v>
       </c>
       <c r="G20" s="47"/>
       <c r="H20" s="47"/>
       <c r="I20" s="40"/>
       <c r="J20" s="25" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="K20" s="15"/>
       <c r="L20" s="15"/>
       <c r="M20" s="41"/>
       <c r="N20" s="6" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="O20" s="15"/>
       <c r="P20" s="15"/>
@@ -10722,40 +10664,40 @@
       </c>
       <c r="C21" s="45"/>
       <c r="D21" s="45" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="F21" s="46" t="s">
+        <v>154</v>
+      </c>
+      <c r="G21" s="25" t="s">
         <v>155</v>
       </c>
-      <c r="G21" s="25" t="s">
+      <c r="H21" s="25" t="s">
         <v>156</v>
-      </c>
-      <c r="H21" s="25" t="s">
-        <v>157</v>
       </c>
       <c r="I21" s="40"/>
       <c r="J21" s="45" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="K21" s="45"/>
       <c r="L21" s="6" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="M21" s="41"/>
       <c r="N21" s="6" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="O21" s="54" t="s">
+        <v>158</v>
+      </c>
+      <c r="P21" s="25" t="s">
         <v>159</v>
       </c>
-      <c r="P21" s="25" t="s">
+      <c r="Q21" s="25" t="s">
         <v>160</v>
-      </c>
-      <c r="Q21" s="25" t="s">
-        <v>161</v>
       </c>
       <c r="R21" s="43"/>
       <c r="S21" s="44"/>
@@ -10774,25 +10716,25 @@
       </c>
       <c r="C22" s="45"/>
       <c r="D22" s="45" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F22" s="46" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="G22" s="47"/>
       <c r="H22" s="47"/>
       <c r="I22" s="40"/>
       <c r="J22" s="6"/>
       <c r="K22" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="L22" s="45"/>
       <c r="M22" s="41"/>
       <c r="N22" s="6" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="O22" s="15"/>
       <c r="P22" s="15"/>
@@ -10814,25 +10756,25 @@
       </c>
       <c r="C23" s="45"/>
       <c r="D23" s="45" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E23" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="F23" s="46" t="s">
         <v>183</v>
-      </c>
-      <c r="F23" s="46" t="s">
-        <v>184</v>
       </c>
       <c r="G23" s="47"/>
       <c r="H23" s="47"/>
       <c r="I23" s="40"/>
       <c r="J23" s="6" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="K23" s="6"/>
       <c r="L23" s="45"/>
       <c r="M23" s="41"/>
       <c r="N23" s="6" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="O23" s="15"/>
       <c r="P23" s="15"/>
@@ -10853,14 +10795,14 @@
         <v>11</v>
       </c>
       <c r="C24" s="51" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="D24" s="51" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E24" s="51"/>
       <c r="F24" s="51" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G24" s="52"/>
       <c r="H24" s="52"/>
@@ -10870,7 +10812,7 @@
       <c r="L24" s="51"/>
       <c r="M24" s="53"/>
       <c r="N24" s="51" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="O24" s="52"/>
       <c r="P24" s="52"/>
@@ -10892,10 +10834,10 @@
       </c>
       <c r="C25" s="45"/>
       <c r="D25" s="45" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="F25" s="46" t="s">
         <v>23</v>
@@ -10908,7 +10850,7 @@
       <c r="L25" s="45"/>
       <c r="M25" s="41"/>
       <c r="N25" s="6" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="O25" s="15"/>
       <c r="P25" s="15"/>
@@ -10930,38 +10872,38 @@
       </c>
       <c r="C26" s="45"/>
       <c r="D26" s="45" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E26" s="45" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F26" s="46" t="s">
         <v>27</v>
       </c>
       <c r="G26" s="56" t="s">
+        <v>188</v>
+      </c>
+      <c r="H26" s="49" t="s">
         <v>189</v>
-      </c>
-      <c r="H26" s="49" t="s">
-        <v>190</v>
       </c>
       <c r="I26" s="40"/>
       <c r="J26" s="57" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="K26" s="58"/>
       <c r="L26" s="58"/>
       <c r="M26" s="41"/>
       <c r="N26" s="45" t="s">
+        <v>191</v>
+      </c>
+      <c r="O26" s="58" t="s">
         <v>192</v>
       </c>
-      <c r="O26" s="58" t="s">
+      <c r="P26" s="17" t="s">
         <v>193</v>
       </c>
-      <c r="P26" s="17" t="s">
+      <c r="Q26" s="17" t="s">
         <v>194</v>
-      </c>
-      <c r="Q26" s="17" t="s">
-        <v>195</v>
       </c>
       <c r="R26" s="43"/>
       <c r="S26" s="59"/>
@@ -10980,25 +10922,25 @@
       </c>
       <c r="C27" s="45"/>
       <c r="D27" s="45" t="s">
+        <v>111</v>
+      </c>
+      <c r="E27" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="F27" s="46" t="s">
         <v>112</v>
-      </c>
-      <c r="E27" s="6" t="s">
-        <v>167</v>
-      </c>
-      <c r="F27" s="46" t="s">
-        <v>113</v>
       </c>
       <c r="G27" s="47"/>
       <c r="H27" s="47"/>
       <c r="I27" s="40"/>
       <c r="J27" s="25" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="K27" s="15"/>
       <c r="L27" s="15"/>
       <c r="M27" s="41"/>
       <c r="N27" s="6" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="O27" s="15"/>
       <c r="P27" s="15"/>
@@ -11020,25 +10962,25 @@
       </c>
       <c r="C28" s="45"/>
       <c r="D28" s="45" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="F28" s="46" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="G28" s="47"/>
       <c r="H28" s="47"/>
       <c r="I28" s="40"/>
       <c r="J28" s="45" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="K28" s="45"/>
       <c r="L28" s="45"/>
       <c r="M28" s="41"/>
       <c r="N28" s="6" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="O28" s="15"/>
       <c r="P28" s="15"/>
@@ -11060,13 +11002,13 @@
       </c>
       <c r="C29" s="45"/>
       <c r="D29" s="45" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E29" s="6" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F29" s="46" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G29" s="47"/>
       <c r="H29" s="47"/>
@@ -11076,7 +11018,7 @@
       <c r="L29" s="45"/>
       <c r="M29" s="41"/>
       <c r="N29" s="6" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="O29" s="15"/>
       <c r="P29" s="15"/>
@@ -11098,25 +11040,25 @@
       </c>
       <c r="C30" s="45"/>
       <c r="D30" s="45" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="F30" s="46" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="G30" s="47"/>
       <c r="H30" s="47"/>
       <c r="I30" s="40"/>
       <c r="J30" s="6" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="K30" s="6"/>
       <c r="L30" s="45"/>
       <c r="M30" s="41"/>
       <c r="N30" s="6" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="O30" s="15"/>
       <c r="P30" s="15"/>
@@ -11158,15 +11100,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <TaxCatchAll xmlns="15fa1163-52ae-44c9-9338-260724b6ed78" xsi:nil="true"/>
@@ -11177,7 +11110,7 @@
 </p:properties>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100D64480D4A3D4144EBDD7ABF44F909263" ma:contentTypeVersion="13" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="a3da3a9da57abd10595da3f4b5bf8a5b">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="65eb73cc-43b1-4677-9773-18a81d166a12" xmlns:ns3="15fa1163-52ae-44c9-9338-260724b6ed78" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="b02162ecf1fb6a41bac9d43297d61488" ns2:_="" ns3:_="">
     <xsd:import namespace="65eb73cc-43b1-4677-9773-18a81d166a12"/>
@@ -11400,32 +11333,33 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E01F75D2-18D7-4457-A217-CD23D85DC8FD}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A8E7B11B-235E-4143-B901-98294EDB0157}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="65eb73cc-43b1-4677-9773-18a81d166a12"/>
+    <ds:schemaRef ds:uri="15fa1163-52ae-44c9-9338-260724b6ed78"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A8E7B11B-235E-4143-B901-98294EDB0157}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="65eb73cc-43b1-4677-9773-18a81d166a12"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="15fa1163-52ae-44c9-9338-260724b6ed78"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD24E4E3-F0C3-4E3F-B0B5-E5CAAF1D49B3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -11442,4 +11376,12 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E01F75D2-18D7-4457-A217-CD23D85DC8FD}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/python-maps/documentation/CDA2FHIR_elga_eMed_groups.xlsx
+++ b/python-maps/documentation/CDA2FHIR_elga_eMed_groups.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/maximilian/Documents/BlackTusk/Bundesrechenzentrum/CDA2FHIR/CDA2FHIR/python-maps/documentation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D6903998-BB95-6D41-A79A-718C304FC4C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{374371A5-9F37-8043-9243-064C66F7F4B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1293" uniqueCount="477">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1293" uniqueCount="475">
   <si>
     <t xml:space="preserve">Status
 </t>
@@ -1371,12 +1371,6 @@
     <t>sA/effectiveTime/period/@unit</t>
   </si>
   <si>
-    <t>sA/effectiveTime/doseQuantity/@value</t>
-  </si>
-  <si>
-    <t>sA/effectiveTime/doseQuantity/@unit</t>
-  </si>
-  <si>
     <t>sA/entryRelationship/@typeCode='COMP'</t>
   </si>
   <si>
@@ -1636,9 +1630,16 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="23" x14ac:knownFonts="1">
+  <fonts count="24" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -2123,167 +2124,167 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="164">
+  <cellXfs count="165">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -2292,252 +2293,253 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="17" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="17" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="17" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="17" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -3125,7 +3127,7 @@
       <c r="K5" s="7"/>
       <c r="L5" s="20"/>
       <c r="M5" s="7" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="N5" s="7"/>
     </row>
@@ -3569,7 +3571,7 @@
         <v>36</v>
       </c>
       <c r="D14" s="84" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="E14" s="82"/>
       <c r="F14" s="87"/>
@@ -3592,7 +3594,7 @@
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A15" s="154" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="B15" s="154"/>
       <c r="C15" s="154"/>
@@ -3619,7 +3621,7 @@
         <v>36</v>
       </c>
       <c r="D16" s="81" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="E16" s="82"/>
       <c r="F16" s="87"/>
@@ -3643,7 +3645,7 @@
         <v>36</v>
       </c>
       <c r="D17" s="97" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="E17" s="82"/>
       <c r="F17" s="87"/>
@@ -3667,7 +3669,7 @@
         <v>36</v>
       </c>
       <c r="D18" s="97" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="E18" s="82"/>
       <c r="F18" s="87"/>
@@ -3691,7 +3693,7 @@
         <v>36</v>
       </c>
       <c r="D19" s="81" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="E19" s="82"/>
       <c r="F19" s="87"/>
@@ -3715,7 +3717,7 @@
         <v>36</v>
       </c>
       <c r="D20" s="81" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="E20" s="82"/>
       <c r="F20" s="87"/>
@@ -3739,7 +3741,7 @@
         <v>36</v>
       </c>
       <c r="D21" s="97" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="E21" s="82"/>
       <c r="F21" s="87"/>
@@ -3763,7 +3765,7 @@
         <v>36</v>
       </c>
       <c r="D22" s="81" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="E22" s="82"/>
       <c r="F22" s="87"/>
@@ -3787,7 +3789,7 @@
         <v>36</v>
       </c>
       <c r="D23" s="81" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="E23" s="82"/>
       <c r="F23" s="87"/>
@@ -3817,14 +3819,14 @@
         <v>36</v>
       </c>
       <c r="D24" s="81" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="E24" s="82"/>
       <c r="F24" s="87"/>
       <c r="G24" s="87"/>
       <c r="H24" s="82"/>
       <c r="I24" s="81" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="J24" s="83" t="s">
         <v>240</v>
@@ -3845,7 +3847,7 @@
         <v>36</v>
       </c>
       <c r="D25" s="81" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="E25" s="82"/>
       <c r="F25" s="87"/>
@@ -3875,7 +3877,7 @@
         <v>36</v>
       </c>
       <c r="D26" s="81" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="E26" s="82"/>
       <c r="F26" s="87"/>
@@ -3903,7 +3905,7 @@
         <v>36</v>
       </c>
       <c r="D27" s="81" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="E27" s="82"/>
       <c r="F27" s="93" t="s">
@@ -3933,7 +3935,7 @@
         <v>36</v>
       </c>
       <c r="D28" s="81" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="E28" s="82"/>
       <c r="F28" s="87"/>
@@ -3957,7 +3959,7 @@
         <v>36</v>
       </c>
       <c r="D29" s="81" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="E29" s="82"/>
       <c r="F29" s="87"/>
@@ -3981,7 +3983,7 @@
         <v>36</v>
       </c>
       <c r="D30" s="81" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="E30" s="82"/>
       <c r="F30" s="87"/>
@@ -4009,7 +4011,7 @@
         <v>36</v>
       </c>
       <c r="D31" s="81" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="E31" s="82"/>
       <c r="F31" s="87"/>
@@ -4033,7 +4035,7 @@
         <v>36</v>
       </c>
       <c r="D32" s="81" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="E32" s="82"/>
       <c r="F32" s="87"/>
@@ -4057,7 +4059,7 @@
         <v>36</v>
       </c>
       <c r="D33" s="81" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="E33" s="82"/>
       <c r="F33" s="87"/>
@@ -4081,7 +4083,7 @@
         <v>36</v>
       </c>
       <c r="D34" s="81" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="E34" s="82"/>
       <c r="F34" s="87"/>
@@ -4111,7 +4113,7 @@
         <v>36</v>
       </c>
       <c r="D35" s="81" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="E35" s="82"/>
       <c r="F35" s="87"/>
@@ -4141,7 +4143,7 @@
         <v>36</v>
       </c>
       <c r="D36" s="81" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="E36" s="82"/>
       <c r="F36" s="87"/>
@@ -4169,7 +4171,7 @@
         <v>36</v>
       </c>
       <c r="D37" s="81" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="E37" s="82"/>
       <c r="F37" s="87" t="s">
@@ -4201,7 +4203,7 @@
         <v>36</v>
       </c>
       <c r="D38" s="81" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="E38" s="82"/>
       <c r="F38" s="87"/>
@@ -4222,7 +4224,7 @@
     </row>
     <row r="39" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A39" s="151" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="B39" s="152"/>
       <c r="C39" s="152"/>
@@ -4246,17 +4248,17 @@
       </c>
       <c r="B40" s="94"/>
       <c r="C40" s="83" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="D40" s="81" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="E40" s="82"/>
       <c r="F40" s="87"/>
       <c r="G40" s="87"/>
       <c r="H40" s="82"/>
       <c r="I40" s="85" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="J40" s="83"/>
       <c r="K40" s="83"/>
@@ -4272,17 +4274,17 @@
       </c>
       <c r="B41" s="94"/>
       <c r="C41" s="83" t="s">
+        <v>466</v>
+      </c>
+      <c r="D41" s="81" t="s">
         <v>468</v>
-      </c>
-      <c r="D41" s="81" t="s">
-        <v>470</v>
       </c>
       <c r="E41" s="82"/>
       <c r="F41" s="87"/>
       <c r="G41" s="87"/>
       <c r="H41" s="82"/>
       <c r="I41" s="85" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="J41" s="83" t="s">
         <v>240</v>
@@ -4444,7 +4446,7 @@
       <c r="K47" s="83"/>
       <c r="L47" s="82"/>
       <c r="M47" s="81" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="N47" s="82"/>
       <c r="O47" s="82"/>
@@ -4470,7 +4472,7 @@
       <c r="K48" s="83"/>
       <c r="L48" s="82"/>
       <c r="M48" s="85" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="N48" s="82"/>
       <c r="O48" s="82"/>
@@ -4646,7 +4648,7 @@
       <c r="K55" s="83"/>
       <c r="L55" s="82"/>
       <c r="M55" s="81" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="N55" s="82"/>
       <c r="O55" s="82"/>
@@ -4672,7 +4674,7 @@
       <c r="K56" s="83"/>
       <c r="L56" s="82"/>
       <c r="M56" s="85" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="N56" s="82"/>
       <c r="O56" s="82"/>
@@ -4984,7 +4986,7 @@
       <c r="G69" s="87"/>
       <c r="H69" s="82"/>
       <c r="I69" s="86" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="J69" s="94"/>
       <c r="K69" s="83"/>
@@ -5434,7 +5436,7 @@
       <c r="G87" s="87"/>
       <c r="H87" s="82"/>
       <c r="I87" s="86" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="J87" s="94"/>
       <c r="K87" s="83"/>
@@ -5857,7 +5859,7 @@
       <c r="K104" s="83"/>
       <c r="L104" s="82"/>
       <c r="M104" s="81" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="N104" s="82"/>
       <c r="O104" s="82"/>
@@ -5887,7 +5889,7 @@
       <c r="K105" s="83"/>
       <c r="L105" s="82"/>
       <c r="M105" s="81" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="N105" s="82"/>
       <c r="O105" s="82"/>
@@ -8271,7 +8273,7 @@
         <v>36</v>
       </c>
       <c r="D199" s="123" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="E199" s="82"/>
       <c r="F199" s="87"/>
@@ -8299,7 +8301,7 @@
         <v>257</v>
       </c>
       <c r="D200" s="123" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="E200" s="82"/>
       <c r="F200" s="93" t="s">
@@ -8331,7 +8333,7 @@
         <v>36</v>
       </c>
       <c r="D201" s="123" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="E201" s="82"/>
       <c r="F201" s="87"/>
@@ -8357,7 +8359,7 @@
         <v>36</v>
       </c>
       <c r="D202" s="123" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="E202" s="82"/>
       <c r="F202" s="87"/>
@@ -8381,7 +8383,7 @@
         <v>36</v>
       </c>
       <c r="D203" s="123" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="E203" s="82"/>
       <c r="F203" s="87"/>
@@ -8409,7 +8411,7 @@
         <v>36</v>
       </c>
       <c r="D204" s="123" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="E204" s="82"/>
       <c r="F204" s="87"/>
@@ -8433,7 +8435,7 @@
         <v>36</v>
       </c>
       <c r="D205" s="123" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="E205" s="82"/>
       <c r="F205" s="87"/>
@@ -8457,7 +8459,7 @@
         <v>36</v>
       </c>
       <c r="D206" s="123" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="E206" s="82"/>
       <c r="F206" s="87" t="s">
@@ -8495,7 +8497,7 @@
         <v>36</v>
       </c>
       <c r="D207" s="123" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="E207" s="82"/>
       <c r="F207" s="87"/>
@@ -8523,7 +8525,7 @@
         <v>36</v>
       </c>
       <c r="D208" s="123" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="E208" s="82"/>
       <c r="F208" s="87"/>
@@ -8551,7 +8553,7 @@
         <v>36</v>
       </c>
       <c r="D209" s="123" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="E209" s="82"/>
       <c r="F209" s="87"/>
@@ -8579,7 +8581,7 @@
         <v>257</v>
       </c>
       <c r="D210" s="123" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="E210" s="82"/>
       <c r="F210" s="93" t="s">
@@ -8663,7 +8665,7 @@
         <v>281</v>
       </c>
       <c r="D213" s="124" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="E213" s="82"/>
       <c r="F213" s="87"/>
@@ -8689,7 +8691,7 @@
         <v>36</v>
       </c>
       <c r="D214" s="125" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="E214" s="82"/>
       <c r="F214" s="87"/>
@@ -8717,7 +8719,7 @@
         <v>36</v>
       </c>
       <c r="D215" s="126" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="E215" s="82"/>
       <c r="F215" s="87"/>
@@ -8745,7 +8747,7 @@
         <v>36</v>
       </c>
       <c r="D216" s="126" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="E216" s="82"/>
       <c r="F216" s="87" t="s">
@@ -8774,8 +8776,8 @@
       <c r="C217" s="115" t="s">
         <v>36</v>
       </c>
-      <c r="D217" s="123" t="s">
-        <v>391</v>
+      <c r="D217" s="164" t="s">
+        <v>432</v>
       </c>
       <c r="E217" s="82"/>
       <c r="F217" s="87"/>
@@ -8802,8 +8804,8 @@
       <c r="C218" s="115" t="s">
         <v>257</v>
       </c>
-      <c r="D218" s="123" t="s">
-        <v>392</v>
+      <c r="D218" s="164" t="s">
+        <v>433</v>
       </c>
       <c r="E218" s="82"/>
       <c r="F218" s="93" t="s">
@@ -8835,7 +8837,7 @@
         <v>36</v>
       </c>
       <c r="D219" s="123" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="E219" s="82"/>
       <c r="F219" s="87"/>
@@ -8861,7 +8863,7 @@
         <v>36</v>
       </c>
       <c r="D220" s="123" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="E220" s="82"/>
       <c r="F220" s="87"/>
@@ -8885,7 +8887,7 @@
         <v>36</v>
       </c>
       <c r="D221" s="123" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="E221" s="82"/>
       <c r="F221" s="87"/>
@@ -8913,7 +8915,7 @@
         <v>36</v>
       </c>
       <c r="D222" s="123" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="E222" s="82"/>
       <c r="F222" s="87"/>
@@ -8937,7 +8939,7 @@
         <v>36</v>
       </c>
       <c r="D223" s="123" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="E223" s="82"/>
       <c r="F223" s="87"/>
@@ -8961,7 +8963,7 @@
         <v>36</v>
       </c>
       <c r="D224" s="123" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="E224" s="82"/>
       <c r="F224" s="87"/>
@@ -8987,7 +8989,7 @@
         <v>36</v>
       </c>
       <c r="D225" s="123" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="E225" s="82"/>
       <c r="F225" s="87"/>
@@ -9013,7 +9015,7 @@
         <v>36</v>
       </c>
       <c r="D226" s="123" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="E226" s="82"/>
       <c r="F226" s="87" t="s">
@@ -9051,7 +9053,7 @@
         <v>36</v>
       </c>
       <c r="D227" s="123" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="E227" s="82"/>
       <c r="F227" s="87"/>
@@ -9079,7 +9081,7 @@
         <v>36</v>
       </c>
       <c r="D228" s="123" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="E228" s="82"/>
       <c r="F228" s="87"/>
@@ -9107,7 +9109,7 @@
         <v>301</v>
       </c>
       <c r="D229" s="123" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="E229" s="82"/>
       <c r="F229" s="87"/>
@@ -9133,7 +9135,7 @@
         <v>36</v>
       </c>
       <c r="D230" s="123" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="E230" s="82"/>
       <c r="F230" s="87"/>
@@ -9161,7 +9163,7 @@
         <v>36</v>
       </c>
       <c r="D231" s="123" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="E231" s="82"/>
       <c r="F231" s="87"/>
@@ -9189,7 +9191,7 @@
         <v>36</v>
       </c>
       <c r="D232" s="123" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="E232" s="82"/>
       <c r="F232" s="87" t="s">
@@ -9219,7 +9221,7 @@
         <v>36</v>
       </c>
       <c r="D233" s="123" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="E233" s="82"/>
       <c r="F233" s="87"/>
@@ -9247,7 +9249,7 @@
         <v>257</v>
       </c>
       <c r="D234" s="123" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="E234" s="82"/>
       <c r="F234" s="93" t="s">
@@ -9277,7 +9279,7 @@
         <v>36</v>
       </c>
       <c r="D235" s="123" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="E235" s="82"/>
       <c r="F235" s="87"/>
@@ -9301,7 +9303,7 @@
         <v>36</v>
       </c>
       <c r="D236" s="123" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="E236" s="82"/>
       <c r="F236" s="87"/>
@@ -9325,7 +9327,7 @@
         <v>36</v>
       </c>
       <c r="D237" s="123" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="E237" s="82"/>
       <c r="F237" s="87"/>
@@ -9349,7 +9351,7 @@
         <v>36</v>
       </c>
       <c r="D238" s="123" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="E238" s="82"/>
       <c r="F238" s="87"/>
@@ -9368,7 +9370,7 @@
     </row>
     <row r="239" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A239" s="154" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="B239" s="154"/>
       <c r="C239" s="154"/>
@@ -9391,13 +9393,13 @@
         <v>26</v>
       </c>
       <c r="B240" s="83" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="C240" s="115" t="s">
         <v>36</v>
       </c>
       <c r="D240" s="81" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="E240" s="82"/>
       <c r="F240" s="87"/>
@@ -9408,7 +9410,7 @@
       <c r="K240" s="83"/>
       <c r="L240" s="83"/>
       <c r="M240" s="81" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="N240" s="82"/>
       <c r="O240" s="82"/>
@@ -9416,7 +9418,7 @@
     </row>
     <row r="241" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A241" s="151" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="B241" s="152"/>
       <c r="C241" s="152"/>
@@ -9439,26 +9441,26 @@
         <v>26</v>
       </c>
       <c r="B242" s="83" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="C242" s="115" t="s">
         <v>36</v>
       </c>
       <c r="D242" s="81" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="E242" s="82"/>
       <c r="F242" s="87"/>
       <c r="G242" s="87"/>
       <c r="H242" s="94"/>
       <c r="I242" s="81" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="J242" s="83"/>
       <c r="K242" s="83"/>
       <c r="L242" s="83"/>
       <c r="M242" s="81" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="N242" s="82"/>
       <c r="O242" s="82"/>
@@ -9466,7 +9468,7 @@
     </row>
     <row r="243" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A243" s="151" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="B243" s="157"/>
       <c r="C243" s="152"/>
@@ -9493,7 +9495,7 @@
         <v>36</v>
       </c>
       <c r="D244" s="123" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="I244" s="123"/>
       <c r="J244" s="144"/>
@@ -9510,7 +9512,7 @@
         <v>36</v>
       </c>
       <c r="D245" s="123" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="I245" s="123"/>
       <c r="J245" s="144"/>
@@ -9527,7 +9529,7 @@
         <v>36</v>
       </c>
       <c r="D246" s="123" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="I246" s="123"/>
       <c r="J246" s="144"/>
@@ -9544,7 +9546,7 @@
         <v>36</v>
       </c>
       <c r="D247" s="123" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="I247" s="123"/>
       <c r="J247" s="144"/>
@@ -9561,7 +9563,7 @@
         <v>36</v>
       </c>
       <c r="D248" s="123" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="I248" s="123" t="s">
         <v>45</v>
@@ -9572,7 +9574,7 @@
       <c r="K248" s="123"/>
       <c r="L248" s="141"/>
       <c r="M248" s="123" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
     </row>
     <row r="249" spans="1:16" x14ac:dyDescent="0.2">
@@ -9600,13 +9602,13 @@
         <v>26</v>
       </c>
       <c r="B250" s="83" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="C250" s="115" t="s">
         <v>36</v>
       </c>
       <c r="D250" s="81" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="E250" s="82"/>
       <c r="F250" s="87"/>
@@ -9617,7 +9619,7 @@
       <c r="K250" s="83"/>
       <c r="L250" s="83"/>
       <c r="M250" s="81" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="N250" s="82"/>
       <c r="O250" s="82"/>
@@ -9648,13 +9650,13 @@
         <v>26</v>
       </c>
       <c r="B252" s="83" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="C252" s="115" t="s">
         <v>36</v>
       </c>
       <c r="D252" s="81" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="E252" s="82"/>
       <c r="F252" s="87"/>
@@ -9665,7 +9667,7 @@
       <c r="K252" s="83"/>
       <c r="L252" s="83"/>
       <c r="M252" s="81" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="N252" s="82"/>
       <c r="O252" s="82"/>
@@ -9696,13 +9698,13 @@
         <v>26</v>
       </c>
       <c r="B254" s="83" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="C254" s="115" t="s">
         <v>36</v>
       </c>
       <c r="D254" s="81" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="E254" s="82"/>
       <c r="F254" s="87"/>
@@ -9713,7 +9715,7 @@
       <c r="K254" s="83"/>
       <c r="L254" s="83"/>
       <c r="M254" s="81" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="N254" s="82"/>
       <c r="O254" s="82"/>
@@ -9744,13 +9746,13 @@
         <v>26</v>
       </c>
       <c r="B256" s="83" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="C256" s="115" t="s">
         <v>36</v>
       </c>
       <c r="D256" s="81" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="E256" s="82"/>
       <c r="F256" s="87"/>
@@ -11345,16 +11347,16 @@
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A8E7B11B-235E-4143-B901-98294EDB0157}">
   <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="65eb73cc-43b1-4677-9773-18a81d166a12"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="15fa1163-52ae-44c9-9338-260724b6ed78"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="65eb73cc-43b1-4677-9773-18a81d166a12"/>
-    <ds:schemaRef ds:uri="15fa1163-52ae-44c9-9338-260724b6ed78"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/python-maps/documentation/CDA2FHIR_elga_eMed_groups.xlsx
+++ b/python-maps/documentation/CDA2FHIR_elga_eMed_groups.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10412"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10419"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/maximilian/Documents/BlackTusk/Bundesrechenzentrum/CDA2FHIR/CDA2FHIR/python-maps/documentation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{374371A5-9F37-8043-9243-064C66F7F4B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{ED6DAA9B-9314-1246-A286-D4E62A3350CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2505,18 +2505,10 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="20" fillId="17" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="20" fillId="17" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="20" fillId="17" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -2524,22 +2516,30 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="17" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="20" fillId="17" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="20" fillId="17" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -3593,21 +3593,21 @@
       <c r="P14" s="82"/>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A15" s="154" t="s">
+      <c r="A15" s="152" t="s">
         <v>441</v>
       </c>
-      <c r="B15" s="154"/>
-      <c r="C15" s="154"/>
-      <c r="D15" s="155"/>
-      <c r="E15" s="155"/>
-      <c r="F15" s="155"/>
-      <c r="G15" s="155"/>
-      <c r="H15" s="154"/>
-      <c r="I15" s="156"/>
-      <c r="J15" s="154"/>
-      <c r="K15" s="154"/>
-      <c r="L15" s="154"/>
-      <c r="M15" s="154"/>
+      <c r="B15" s="152"/>
+      <c r="C15" s="152"/>
+      <c r="D15" s="153"/>
+      <c r="E15" s="153"/>
+      <c r="F15" s="153"/>
+      <c r="G15" s="153"/>
+      <c r="H15" s="152"/>
+      <c r="I15" s="154"/>
+      <c r="J15" s="152"/>
+      <c r="K15" s="152"/>
+      <c r="L15" s="152"/>
+      <c r="M15" s="152"/>
       <c r="N15" s="82"/>
       <c r="O15" s="82"/>
       <c r="P15" s="82"/>
@@ -4223,19 +4223,19 @@
       <c r="P38" s="82"/>
     </row>
     <row r="39" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A39" s="151" t="s">
+      <c r="A39" s="158" t="s">
         <v>442</v>
       </c>
-      <c r="B39" s="152"/>
-      <c r="C39" s="152"/>
-      <c r="D39" s="152"/>
-      <c r="E39" s="152"/>
-      <c r="F39" s="152"/>
-      <c r="G39" s="152"/>
-      <c r="H39" s="152"/>
-      <c r="I39" s="152"/>
-      <c r="J39" s="152"/>
-      <c r="K39" s="153"/>
+      <c r="B39" s="159"/>
+      <c r="C39" s="159"/>
+      <c r="D39" s="159"/>
+      <c r="E39" s="159"/>
+      <c r="F39" s="159"/>
+      <c r="G39" s="159"/>
+      <c r="H39" s="159"/>
+      <c r="I39" s="159"/>
+      <c r="J39" s="159"/>
+      <c r="K39" s="160"/>
       <c r="L39" s="100"/>
       <c r="M39" s="100"/>
       <c r="N39" s="82"/>
@@ -4479,19 +4479,19 @@
       <c r="P48" s="82"/>
     </row>
     <row r="49" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A49" s="151" t="s">
+      <c r="A49" s="158" t="s">
         <v>201</v>
       </c>
-      <c r="B49" s="152"/>
-      <c r="C49" s="152"/>
-      <c r="D49" s="152"/>
-      <c r="E49" s="152"/>
-      <c r="F49" s="152"/>
-      <c r="G49" s="152"/>
-      <c r="H49" s="152"/>
-      <c r="I49" s="152"/>
-      <c r="J49" s="152"/>
-      <c r="K49" s="152"/>
+      <c r="B49" s="159"/>
+      <c r="C49" s="159"/>
+      <c r="D49" s="159"/>
+      <c r="E49" s="159"/>
+      <c r="F49" s="159"/>
+      <c r="G49" s="159"/>
+      <c r="H49" s="159"/>
+      <c r="I49" s="159"/>
+      <c r="J49" s="159"/>
+      <c r="K49" s="159"/>
       <c r="L49" s="101"/>
       <c r="M49" s="100"/>
       <c r="N49" s="82"/>
@@ -4681,21 +4681,21 @@
       <c r="P56" s="82"/>
     </row>
     <row r="57" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A57" s="159" t="s">
+      <c r="A57" s="155" t="s">
         <v>202</v>
       </c>
-      <c r="B57" s="149"/>
-      <c r="C57" s="149"/>
-      <c r="D57" s="149"/>
-      <c r="E57" s="149"/>
-      <c r="F57" s="149"/>
-      <c r="G57" s="149"/>
-      <c r="H57" s="149"/>
-      <c r="I57" s="160"/>
-      <c r="J57" s="160"/>
-      <c r="K57" s="160"/>
-      <c r="L57" s="149"/>
-      <c r="M57" s="161"/>
+      <c r="B57" s="150"/>
+      <c r="C57" s="150"/>
+      <c r="D57" s="150"/>
+      <c r="E57" s="150"/>
+      <c r="F57" s="150"/>
+      <c r="G57" s="150"/>
+      <c r="H57" s="150"/>
+      <c r="I57" s="156"/>
+      <c r="J57" s="156"/>
+      <c r="K57" s="156"/>
+      <c r="L57" s="150"/>
+      <c r="M57" s="157"/>
       <c r="N57" s="82"/>
       <c r="O57" s="82"/>
       <c r="P57" s="82"/>
@@ -4788,10 +4788,10 @@
       <c r="G61" s="103"/>
       <c r="H61" s="103"/>
       <c r="I61" s="102"/>
-      <c r="J61" s="148"/>
-      <c r="K61" s="148"/>
-      <c r="L61" s="149"/>
-      <c r="M61" s="150"/>
+      <c r="J61" s="149"/>
+      <c r="K61" s="149"/>
+      <c r="L61" s="150"/>
+      <c r="M61" s="151"/>
       <c r="N61" s="82"/>
       <c r="O61" s="82"/>
       <c r="P61" s="82"/>
@@ -5237,10 +5237,10 @@
       <c r="G79" s="103"/>
       <c r="H79" s="103"/>
       <c r="I79" s="102"/>
-      <c r="J79" s="148"/>
-      <c r="K79" s="148"/>
-      <c r="L79" s="149"/>
-      <c r="M79" s="150"/>
+      <c r="J79" s="149"/>
+      <c r="K79" s="149"/>
+      <c r="L79" s="150"/>
+      <c r="M79" s="151"/>
       <c r="N79" s="82"/>
       <c r="O79" s="82"/>
       <c r="P79" s="82"/>
@@ -8776,7 +8776,7 @@
       <c r="C217" s="115" t="s">
         <v>36</v>
       </c>
-      <c r="D217" s="164" t="s">
+      <c r="D217" s="148" t="s">
         <v>432</v>
       </c>
       <c r="E217" s="82"/>
@@ -8804,7 +8804,7 @@
       <c r="C218" s="115" t="s">
         <v>257</v>
       </c>
-      <c r="D218" s="164" t="s">
+      <c r="D218" s="148" t="s">
         <v>433</v>
       </c>
       <c r="E218" s="82"/>
@@ -9369,21 +9369,21 @@
       <c r="P238" s="18"/>
     </row>
     <row r="239" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A239" s="154" t="s">
+      <c r="A239" s="152" t="s">
         <v>441</v>
       </c>
-      <c r="B239" s="154"/>
-      <c r="C239" s="154"/>
-      <c r="D239" s="155"/>
-      <c r="E239" s="155"/>
-      <c r="F239" s="155"/>
-      <c r="G239" s="155"/>
-      <c r="H239" s="154"/>
-      <c r="I239" s="156"/>
-      <c r="J239" s="154"/>
-      <c r="K239" s="154"/>
-      <c r="L239" s="154"/>
-      <c r="M239" s="154"/>
+      <c r="B239" s="152"/>
+      <c r="C239" s="152"/>
+      <c r="D239" s="153"/>
+      <c r="E239" s="153"/>
+      <c r="F239" s="153"/>
+      <c r="G239" s="153"/>
+      <c r="H239" s="152"/>
+      <c r="I239" s="154"/>
+      <c r="J239" s="152"/>
+      <c r="K239" s="152"/>
+      <c r="L239" s="152"/>
+      <c r="M239" s="152"/>
       <c r="N239" s="82"/>
       <c r="O239" s="82"/>
       <c r="P239" s="82"/>
@@ -9417,19 +9417,19 @@
       <c r="P240" s="82"/>
     </row>
     <row r="241" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A241" s="151" t="s">
+      <c r="A241" s="158" t="s">
         <v>442</v>
       </c>
-      <c r="B241" s="152"/>
-      <c r="C241" s="152"/>
-      <c r="D241" s="152"/>
-      <c r="E241" s="152"/>
-      <c r="F241" s="152"/>
-      <c r="G241" s="152"/>
-      <c r="H241" s="152"/>
-      <c r="I241" s="152"/>
-      <c r="J241" s="152"/>
-      <c r="K241" s="153"/>
+      <c r="B241" s="159"/>
+      <c r="C241" s="159"/>
+      <c r="D241" s="159"/>
+      <c r="E241" s="159"/>
+      <c r="F241" s="159"/>
+      <c r="G241" s="159"/>
+      <c r="H241" s="159"/>
+      <c r="I241" s="159"/>
+      <c r="J241" s="159"/>
+      <c r="K241" s="160"/>
       <c r="L241" s="100"/>
       <c r="M241" s="100"/>
       <c r="N241" s="82"/>
@@ -9467,19 +9467,19 @@
       <c r="P242" s="82"/>
     </row>
     <row r="243" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A243" s="151" t="s">
+      <c r="A243" s="158" t="s">
         <v>448</v>
       </c>
-      <c r="B243" s="157"/>
-      <c r="C243" s="152"/>
-      <c r="D243" s="152"/>
-      <c r="E243" s="152"/>
-      <c r="F243" s="152"/>
-      <c r="G243" s="152"/>
-      <c r="H243" s="152"/>
-      <c r="I243" s="157"/>
-      <c r="J243" s="157"/>
-      <c r="K243" s="158"/>
+      <c r="B243" s="161"/>
+      <c r="C243" s="159"/>
+      <c r="D243" s="159"/>
+      <c r="E243" s="159"/>
+      <c r="F243" s="159"/>
+      <c r="G243" s="159"/>
+      <c r="H243" s="159"/>
+      <c r="I243" s="161"/>
+      <c r="J243" s="161"/>
+      <c r="K243" s="162"/>
       <c r="L243" s="140"/>
       <c r="M243" s="140"/>
       <c r="N243" s="82"/>
@@ -9589,10 +9589,10 @@
       <c r="G249" s="103"/>
       <c r="H249" s="103"/>
       <c r="I249" s="102"/>
-      <c r="J249" s="148"/>
-      <c r="K249" s="148"/>
-      <c r="L249" s="149"/>
-      <c r="M249" s="150"/>
+      <c r="J249" s="149"/>
+      <c r="K249" s="149"/>
+      <c r="L249" s="150"/>
+      <c r="M249" s="151"/>
       <c r="N249" s="82"/>
       <c r="O249" s="82"/>
       <c r="P249" s="82"/>
@@ -9637,10 +9637,10 @@
       <c r="G251" s="103"/>
       <c r="H251" s="103"/>
       <c r="I251" s="102"/>
-      <c r="J251" s="148"/>
-      <c r="K251" s="148"/>
-      <c r="L251" s="149"/>
-      <c r="M251" s="150"/>
+      <c r="J251" s="149"/>
+      <c r="K251" s="149"/>
+      <c r="L251" s="150"/>
+      <c r="M251" s="151"/>
       <c r="N251" s="82"/>
       <c r="O251" s="82"/>
       <c r="P251" s="82"/>
@@ -9771,17 +9771,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="J251:M251"/>
+    <mergeCell ref="A241:K241"/>
+    <mergeCell ref="A239:M239"/>
+    <mergeCell ref="A243:K243"/>
+    <mergeCell ref="J249:M249"/>
     <mergeCell ref="J79:M79"/>
     <mergeCell ref="A15:M15"/>
     <mergeCell ref="A57:M57"/>
     <mergeCell ref="J61:M61"/>
     <mergeCell ref="A39:K39"/>
     <mergeCell ref="A49:K49"/>
-    <mergeCell ref="J251:M251"/>
-    <mergeCell ref="A241:K241"/>
-    <mergeCell ref="A239:M239"/>
-    <mergeCell ref="A243:K243"/>
-    <mergeCell ref="J249:M249"/>
   </mergeCells>
   <conditionalFormatting sqref="A1:A56 A58:A60 A62:A78 A80:A96 A98:A151 A153:A158 A181:A193 A195:A248 A250 A252 A254 A256:A1048576">
     <cfRule type="cellIs" dxfId="10" priority="17" operator="equal">
@@ -9840,12 +9840,12 @@
     <row r="1" spans="1:26" ht="20" x14ac:dyDescent="0.2">
       <c r="A1" s="26"/>
       <c r="B1" s="27"/>
-      <c r="C1" s="162" t="s">
+      <c r="C1" s="163" t="s">
         <v>105</v>
       </c>
-      <c r="D1" s="162"/>
-      <c r="E1" s="163"/>
-      <c r="F1" s="163"/>
+      <c r="D1" s="163"/>
+      <c r="E1" s="164"/>
+      <c r="F1" s="164"/>
       <c r="I1" s="26"/>
       <c r="J1" s="28"/>
       <c r="K1" s="28"/>
@@ -11102,14 +11102,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="15fa1163-52ae-44c9-9338-260724b6ed78" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="65eb73cc-43b1-4677-9773-18a81d166a12">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -11336,27 +11334,20 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="15fa1163-52ae-44c9-9338-260724b6ed78" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="65eb73cc-43b1-4677-9773-18a81d166a12">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A8E7B11B-235E-4143-B901-98294EDB0157}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E01F75D2-18D7-4457-A217-CD23D85DC8FD}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="65eb73cc-43b1-4677-9773-18a81d166a12"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="15fa1163-52ae-44c9-9338-260724b6ed78"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -11381,9 +11372,18 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E01F75D2-18D7-4457-A217-CD23D85DC8FD}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A8E7B11B-235E-4143-B901-98294EDB0157}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="65eb73cc-43b1-4677-9773-18a81d166a12"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="15fa1163-52ae-44c9-9338-260724b6ed78"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>